--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB94F5-528B-4FF6-96DA-15B0BCBBBEDD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3836967F-B75E-4526-88FA-92217ED66D6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="62" activeTab="63" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="71" activeTab="73" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -72,10 +72,20 @@
     <sheet name="IP_Credit_Limit" sheetId="79" r:id="rId62"/>
     <sheet name="IP_General_OrderEntry" sheetId="80" r:id="rId63"/>
     <sheet name="Ip_Doctor_Vist_Page" sheetId="86" r:id="rId64"/>
-    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId65"/>
-    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId66"/>
-    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId67"/>
-    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId68"/>
+    <sheet name="Ip_Billing_Page" sheetId="87" r:id="rId65"/>
+    <sheet name="Ip_Bill_Add_on_Bill" sheetId="89" r:id="rId66"/>
+    <sheet name="Due_Settlement_Page" sheetId="90" r:id="rId67"/>
+    <sheet name="Ip_DepositRefund_Page" sheetId="91" r:id="rId68"/>
+    <sheet name="Ip_Refund_Page" sheetId="92" r:id="rId69"/>
+    <sheet name="Ip_ReceiptUtility_Page" sheetId="93" r:id="rId70"/>
+    <sheet name="OP_Deposit_Transfer_Ip" sheetId="94" r:id="rId71"/>
+    <sheet name="IP_Cheque_In_HandDetails" sheetId="95" r:id="rId72"/>
+    <sheet name="IP_Cheque_In_Hand" sheetId="96" r:id="rId73"/>
+    <sheet name="Package_Duration_Modifiction" sheetId="97" r:id="rId74"/>
+    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId75"/>
+    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId76"/>
+    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId77"/>
+    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId78"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -87,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="1197">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -3069,6 +3079,615 @@
   </si>
   <si>
     <t>Eter_Search_To_Date</t>
+  </si>
+  <si>
+    <t>Discharge_Type_Drp</t>
+  </si>
+  <si>
+    <t>Discharge_Sub_Type_Drp</t>
+  </si>
+  <si>
+    <t>Discharge_Remarks_Text</t>
+  </si>
+  <si>
+    <t>Anup Discharge Remarks</t>
+  </si>
+  <si>
+    <t>Discharge on Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPSL..885723 </t>
+  </si>
+  <si>
+    <t>Enter_UHID_All_Clearance</t>
+  </si>
+  <si>
+    <t>Enter_IP_Number_All_Clearance</t>
+  </si>
+  <si>
+    <t>SPSL.85457</t>
+  </si>
+  <si>
+    <t>Discharge_Reason_Drp</t>
+  </si>
+  <si>
+    <t>Discharge_Remarks</t>
+  </si>
+  <si>
+    <t>Taylor Swift's Eras Tour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anup Discharge Icon </t>
+  </si>
+  <si>
+    <t>Company_type_Drp</t>
+  </si>
+  <si>
+    <t>Policy_Number</t>
+  </si>
+  <si>
+    <t>Auth_Claim_no</t>
+  </si>
+  <si>
+    <t>Standard_Deductible</t>
+  </si>
+  <si>
+    <t>Standard_Co_pay_Drp</t>
+  </si>
+  <si>
+    <t>Co_Pay_Text</t>
+  </si>
+  <si>
+    <t>Letter_no</t>
+  </si>
+  <si>
+    <t>Letter_Date</t>
+  </si>
+  <si>
+    <t>Employee_Number</t>
+  </si>
+  <si>
+    <t>Certificate_number</t>
+  </si>
+  <si>
+    <t>Bed_Entitlement</t>
+  </si>
+  <si>
+    <t>Per_Day</t>
+  </si>
+  <si>
+    <t>Account_Number</t>
+  </si>
+  <si>
+    <t>IFSC_Code</t>
+  </si>
+  <si>
+    <t>Bank_Branch</t>
+  </si>
+  <si>
+    <t>PAN_No</t>
+  </si>
+  <si>
+    <t>Insurance_Company_Drp</t>
+  </si>
+  <si>
+    <t>Auth_Amount</t>
+  </si>
+  <si>
+    <t>Credit_Limit</t>
+  </si>
+  <si>
+    <t>Employee_Code</t>
+  </si>
+  <si>
+    <t>Employee_Relation</t>
+  </si>
+  <si>
+    <t>Issued_By</t>
+  </si>
+  <si>
+    <t>Anup001</t>
+  </si>
+  <si>
+    <t>kumar002</t>
+  </si>
+  <si>
+    <t>PUNB0854</t>
+  </si>
+  <si>
+    <t>Fibroscan Scheme</t>
+  </si>
+  <si>
+    <t>BADR ALL SHEMA</t>
+  </si>
+  <si>
+    <t>NO Data</t>
+  </si>
+  <si>
+    <t>Anup99</t>
+  </si>
+  <si>
+    <t>Surgery_To_Date</t>
+  </si>
+  <si>
+    <t>Surgery_From_Date</t>
+  </si>
+  <si>
+    <t>Bill_Genrate_Reason_Text</t>
+  </si>
+  <si>
+    <t>Anup Bill Genrate Reason</t>
+  </si>
+  <si>
+    <t>Bill_Settlement_Reason_Text</t>
+  </si>
+  <si>
+    <t>Bill Settlement Reason Anup</t>
+  </si>
+  <si>
+    <t>Bill_Settlement_Remarks</t>
+  </si>
+  <si>
+    <t>Bill Settlement Remarks</t>
+  </si>
+  <si>
+    <t>Received_From_Bill_Settl</t>
+  </si>
+  <si>
+    <t>Cheque_Branch</t>
+  </si>
+  <si>
+    <t>Cheque_Amount</t>
+  </si>
+  <si>
+    <t>Cheque_Authorised_By_Drp</t>
+  </si>
+  <si>
+    <t>Bill_Amount</t>
+  </si>
+  <si>
+    <t>Due_Authorised_By_Drp</t>
+  </si>
+  <si>
+    <t>Jai Singh</t>
+  </si>
+  <si>
+    <t>Due_Remarks</t>
+  </si>
+  <si>
+    <t>Due Remarks Anup</t>
+  </si>
+  <si>
+    <t>Cancel_Bill_Settl_Authorised</t>
+  </si>
+  <si>
+    <t>Cancel_Bill_Settl_Remaks</t>
+  </si>
+  <si>
+    <t>Cancel Bill Settle Remaks</t>
+  </si>
+  <si>
+    <t>MOU Discount</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>GENERAL WARD (SEVENTH FLOOR)</t>
+  </si>
+  <si>
+    <t>Alloted_bed_type_drp</t>
+  </si>
+  <si>
+    <t>ICU</t>
+  </si>
+  <si>
+    <t>Enter_Bill_Number</t>
+  </si>
+  <si>
+    <t>Enter_Amount</t>
+  </si>
+  <si>
+    <t>Rounding_Off_Settlement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPDI232915	</t>
+  </si>
+  <si>
+    <t>Entet_Cheque_Number</t>
+  </si>
+  <si>
+    <t>Cheque_Date</t>
+  </si>
+  <si>
+    <t>Enter_Credit_Card_Number</t>
+  </si>
+  <si>
+    <t>Enter_Transtion_No</t>
+  </si>
+  <si>
+    <t>Credit_Card_Amount</t>
+  </si>
+  <si>
+    <t>VISA</t>
+  </si>
+  <si>
+    <t>Debit_Card_Numbetr</t>
+  </si>
+  <si>
+    <t>Debit_Card_Type_Drp</t>
+  </si>
+  <si>
+    <t>Debit_Card_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>Enter_Debit_Card_Transtion_No</t>
+  </si>
+  <si>
+    <t>Debit_Card_Amount</t>
+  </si>
+  <si>
+    <t>ALLAHABAD BANK</t>
+  </si>
+  <si>
+    <t>Enter_Discount_Amount</t>
+  </si>
+  <si>
+    <t>Discount_Head_Name_Drp</t>
+  </si>
+  <si>
+    <t>Discount_Reason_Drp_Drp</t>
+  </si>
+  <si>
+    <t>Discount_Enter_Remarks</t>
+  </si>
+  <si>
+    <t>Discount_Authorised_Drp</t>
+  </si>
+  <si>
+    <t>Capitation Discount</t>
+  </si>
+  <si>
+    <t>Discount Reamks</t>
+  </si>
+  <si>
+    <t>NEFT_Trans_No</t>
+  </si>
+  <si>
+    <t>NEFT_Trans_Date</t>
+  </si>
+  <si>
+    <t>NEFT_Bank_Drp</t>
+  </si>
+  <si>
+    <t>NEFT_Branch_Name</t>
+  </si>
+  <si>
+    <t>NEFT_Enter_Amount</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Others_Payment_Type_Drp</t>
+  </si>
+  <si>
+    <t>Other_payment_Transaction_Number</t>
+  </si>
+  <si>
+    <t>Other_Payment_RRN_Number</t>
+  </si>
+  <si>
+    <t>Other_Payment_Remarks</t>
+  </si>
+  <si>
+    <t>Other_Payment_Amount</t>
+  </si>
+  <si>
+    <t>Availed Company Deposit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Opthers Payment </t>
+  </si>
+  <si>
+    <t>Enter_Received_From</t>
+  </si>
+  <si>
+    <t>Enter_Due_Settlement_Remarks</t>
+  </si>
+  <si>
+    <t>Final Remarks</t>
+  </si>
+  <si>
+    <t>Company_From_Date</t>
+  </si>
+  <si>
+    <t>Company_To_Date</t>
+  </si>
+  <si>
+    <t>Divyanshu</t>
+  </si>
+  <si>
+    <t>Enter_IP_Number_Excel_Sheet</t>
+  </si>
+  <si>
+    <t>Enter_Deposit_Remarks</t>
+  </si>
+  <si>
+    <t>Select_Relationship_Drp</t>
+  </si>
+  <si>
+    <t>Anup Ip Deposit</t>
+  </si>
+  <si>
+    <t>Cheque_Bank_Branch</t>
+  </si>
+  <si>
+    <t>ABN AMRO BANK</t>
+  </si>
+  <si>
+    <t>Credit_Card_No</t>
+  </si>
+  <si>
+    <t>Credit_Type_Drp</t>
+  </si>
+  <si>
+    <t>Credit_Bank_Drp</t>
+  </si>
+  <si>
+    <t>Credit_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Credit_Amount</t>
+  </si>
+  <si>
+    <t>Debit_Card_No</t>
+  </si>
+  <si>
+    <t>Debit_Type_Drp</t>
+  </si>
+  <si>
+    <t>Debit_Bank_Drp</t>
+  </si>
+  <si>
+    <t>Debit_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Debit_Amount</t>
+  </si>
+  <si>
+    <t>DINERS</t>
+  </si>
+  <si>
+    <t>NEFT_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Enter_NEFT_Date</t>
+  </si>
+  <si>
+    <t>NEFT_Bank_Branch</t>
+  </si>
+  <si>
+    <t>NEFT_Amount</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Other_Mode_Of_Payment_Drp</t>
+  </si>
+  <si>
+    <t>Other_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Other_RRN_Number</t>
+  </si>
+  <si>
+    <t>Other_Remarks</t>
+  </si>
+  <si>
+    <t>Other_Amount</t>
+  </si>
+  <si>
+    <t>Gpay</t>
+  </si>
+  <si>
+    <t>Anup Other Deposit</t>
+  </si>
+  <si>
+    <t>Refund_Amount_Excel</t>
+  </si>
+  <si>
+    <t>Payable_Name_Excel</t>
+  </si>
+  <si>
+    <t>Refund_Remarks_Excel</t>
+  </si>
+  <si>
+    <t>Refund Remaks Anup</t>
+  </si>
+  <si>
+    <t>IP_Deposit_Refund</t>
+  </si>
+  <si>
+    <t>Refund_Cheque_Number</t>
+  </si>
+  <si>
+    <t>Refund_Cheque_Date</t>
+  </si>
+  <si>
+    <t>Refund_Cheque_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>Refund_Cheque_Bank_Branch</t>
+  </si>
+  <si>
+    <t>Refund_Cheque_Amount</t>
+  </si>
+  <si>
+    <t>Account_No</t>
+  </si>
+  <si>
+    <t>Account_Holder_Name</t>
+  </si>
+  <si>
+    <t>Account_Type</t>
+  </si>
+  <si>
+    <t>Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>Branch_Name</t>
+  </si>
+  <si>
+    <t>Processing_Finance_NEFT_Amount</t>
+  </si>
+  <si>
+    <t>Saving</t>
+  </si>
+  <si>
+    <t>Punb04521</t>
+  </si>
+  <si>
+    <t>Refund_Credit_Card_No</t>
+  </si>
+  <si>
+    <t>Refund_Credit_Type_Drp</t>
+  </si>
+  <si>
+    <t>Refund_Credit_Bank_Drp</t>
+  </si>
+  <si>
+    <t>Refund_Credit_Batch_No</t>
+  </si>
+  <si>
+    <t>Refund_Credit_Amount</t>
+  </si>
+  <si>
+    <t>AMRICAN EXPRESS</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Transaction_No</t>
+  </si>
+  <si>
+    <t>Trans_Date_Enter</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Branch_Name</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_NEFT_Amount</t>
+  </si>
+  <si>
+    <t>Refund_Other_Mode_Of_Payment_Drp</t>
+  </si>
+  <si>
+    <t>Refund_Other_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Refund_Other_RRN_Number</t>
+  </si>
+  <si>
+    <t>Refund_Other_Amount</t>
+  </si>
+  <si>
+    <t>Corporate Collection</t>
+  </si>
+  <si>
+    <t>Find_Patint_From_Date</t>
+  </si>
+  <si>
+    <t>Find_Patient_To_Date</t>
+  </si>
+  <si>
+    <t>Receipt_Ip_Number_Excel_Sheet</t>
+  </si>
+  <si>
+    <t>Receipt_Recept_Number_Excel_Sheet</t>
+  </si>
+  <si>
+    <t>IPDP2103</t>
+  </si>
+  <si>
+    <t>Receipt_Frome_Date</t>
+  </si>
+  <si>
+    <t>Facility_Drp</t>
+  </si>
+  <si>
+    <t>FRONT OFFICE</t>
+  </si>
+  <si>
+    <t>Anup Op To Ip Transfer</t>
+  </si>
+  <si>
+    <t>Op_Deposit_Amount</t>
+  </si>
+  <si>
+    <t>SPSL.885844</t>
+  </si>
+  <si>
+    <t>SPSL.885847</t>
+  </si>
+  <si>
+    <t>Cheque_From_Date</t>
+  </si>
+  <si>
+    <t>Cheque_To_Date</t>
+  </si>
+  <si>
+    <t>Patient_Search_From_Date</t>
+  </si>
+  <si>
+    <t>Patient_Search_To_Date</t>
+  </si>
+  <si>
+    <t>Cheque_Amount_Text</t>
+  </si>
+  <si>
+    <t>Cheque_Number_Text</t>
+  </si>
+  <si>
+    <t>Cheque_Date_Text</t>
+  </si>
+  <si>
+    <t>Bank_Name_DropDwon</t>
+  </si>
+  <si>
+    <t>Bank_Branch_Text</t>
+  </si>
+  <si>
+    <t>Cheque_Remarks_Text</t>
+  </si>
+  <si>
+    <t>Anup Cheque Remarks</t>
+  </si>
+  <si>
+    <t>Enter_Ip_Number_Excel</t>
+  </si>
+  <si>
+    <t>SPSL.885851</t>
+  </si>
+  <si>
+    <t>Change_Billable_Bed_Type_Drn</t>
+  </si>
+  <si>
+    <t>EMERGENCY1</t>
+  </si>
+  <si>
+    <t>Package_Chargeable_Percentage</t>
+  </si>
+  <si>
+    <t>Package_Doctor_Speciality</t>
+  </si>
+  <si>
+    <t>Package_Doctor_Name</t>
+  </si>
+  <si>
+    <t>Himanshu Sharma Cardiologist</t>
   </si>
 </sst>
 </file>
@@ -7848,13 +8467,15 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F9016A-938F-4400-83E8-235BA46C870F}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>768</v>
       </c>
@@ -7904,28 +8525,31 @@
         <v>782</v>
       </c>
       <c r="Q1" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -7966,7 +8590,7 @@
         <v>378</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>797</v>
+        <v>1057</v>
       </c>
       <c r="O2" s="11" t="s">
         <v>798</v>
@@ -7975,24 +8599,27 @@
         <v>799</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>800</v>
+        <v>1060</v>
       </c>
       <c r="R2" s="11" t="s">
+        <v>1058</v>
+      </c>
+      <c r="S2" s="11" t="s">
         <v>796</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>801</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>801</v>
       </c>
     </row>
@@ -10097,7 +10724,7 @@
         <v>948</v>
       </c>
       <c r="N2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="O2">
         <v>2</v>
@@ -10677,149 +11304,421 @@
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F09270-1FEE-4D7E-A2B1-067B6E58EC0B}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FB2B9F-5C63-4573-B0FF-F4AA329DC337}">
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="24" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="15" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="12" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>900</v>
       </c>
       <c r="B1" t="s">
-        <v>975</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>921</v>
+        <v>422</v>
       </c>
       <c r="D1" t="s">
-        <v>976</v>
+        <v>423</v>
       </c>
       <c r="E1" t="s">
-        <v>977</v>
+        <v>932</v>
       </c>
       <c r="F1" t="s">
-        <v>952</v>
+        <v>934</v>
       </c>
       <c r="G1" t="s">
-        <v>978</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="N1" t="s">
+        <v>424</v>
+      </c>
+      <c r="O1" t="s">
+        <v>751</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>497</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>242</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>800</v>
-      </c>
-      <c r="C2" t="s">
-        <v>523</v>
+        <v>908</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46054</v>
       </c>
       <c r="D2" s="1">
-        <v>46055</v>
-      </c>
-      <c r="E2" t="s">
-        <v>848</v>
-      </c>
-      <c r="F2">
-        <v>29344</v>
+        <v>46062</v>
+      </c>
+      <c r="E2">
+        <v>9876543210</v>
+      </c>
+      <c r="F2" t="s">
+        <v>933</v>
       </c>
       <c r="G2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46025</v>
+        <v>999</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I2">
+        <v>29387</v>
+      </c>
+      <c r="J2" t="s">
+        <v>815</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="M2" t="s">
+        <v>214</v>
+      </c>
+      <c r="N2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O2" t="s">
+        <v>216</v>
+      </c>
+      <c r="P2">
+        <v>111</v>
+      </c>
+      <c r="Q2">
+        <v>222</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
+        <v>875</v>
+      </c>
+      <c r="T2">
+        <v>500</v>
+      </c>
+      <c r="U2">
+        <v>333</v>
+      </c>
+      <c r="V2" s="1">
+        <v>46063</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="Y2">
+        <v>2000</v>
+      </c>
+      <c r="Z2">
+        <v>100</v>
+      </c>
+      <c r="AA2">
+        <v>963852741</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>741852963</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AH2">
+        <v>6000</v>
+      </c>
+      <c r="AI2">
+        <v>5</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>46063</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>46062</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46063</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS2">
+        <v>963852741</v>
+      </c>
+      <c r="AT2" s="1">
+        <v>46063</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW2">
+        <v>1000</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>510</v>
+      </c>
+      <c r="AY2">
+        <v>500</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>1055</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6946A-E358-4DE2-B43D-AD5F7808634C}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D418190-A307-409C-9B13-520CE3406CF2}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>900</v>
       </c>
-      <c r="B1" t="s">
-        <v>980</v>
-      </c>
-      <c r="C1" t="s">
-        <v>920</v>
-      </c>
-      <c r="D1" t="s">
-        <v>982</v>
-      </c>
-      <c r="E1" t="s">
-        <v>976</v>
-      </c>
-      <c r="F1" t="s">
-        <v>977</v>
-      </c>
-      <c r="G1" t="s">
-        <v>952</v>
-      </c>
-      <c r="H1" t="s">
-        <v>978</v>
-      </c>
-      <c r="I1" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>981</v>
-      </c>
-      <c r="C2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46054</v>
-      </c>
-      <c r="F2" t="s">
-        <v>848</v>
-      </c>
-      <c r="G2">
-        <v>29344</v>
-      </c>
-      <c r="H2" t="s">
-        <v>910</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46057</v>
       </c>
     </row>
   </sheetData>
@@ -10828,70 +11727,559 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753D503-B7CA-43F7-BD19-60134A1E726F}">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB81613-B25D-46A1-9C96-7C4B253B73B9}">
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="19.28515625" customWidth="1"/>
+    <col min="27" max="27" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="24" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="30.5703125" customWidth="1"/>
+    <col min="40" max="40" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>900</v>
       </c>
       <c r="B1" t="s">
-        <v>980</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>921</v>
+        <v>450</v>
       </c>
       <c r="D1" t="s">
-        <v>976</v>
+        <v>1061</v>
       </c>
       <c r="E1" t="s">
-        <v>977</v>
+        <v>1062</v>
       </c>
       <c r="F1" t="s">
-        <v>952</v>
+        <v>1063</v>
       </c>
       <c r="G1" t="s">
-        <v>978</v>
+        <v>1065</v>
       </c>
       <c r="H1" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1066</v>
+      </c>
+      <c r="I1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J1" t="s">
+        <v>499</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="M1" t="s">
+        <v>501</v>
+      </c>
+      <c r="N1" t="s">
+        <v>557</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C2" t="s">
-        <v>523</v>
+        <v>908</v>
+      </c>
+      <c r="C2">
+        <v>29402</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>987654321</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46066</v>
+      </c>
+      <c r="I2" t="s">
+        <v>246</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>50</v>
+      </c>
+      <c r="L2">
+        <v>3216549787</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="N2" t="s">
+        <v>246</v>
+      </c>
+      <c r="O2">
+        <v>8574</v>
+      </c>
+      <c r="P2">
+        <v>60</v>
+      </c>
+      <c r="Q2">
+        <v>852741</v>
+      </c>
+      <c r="R2" t="s">
+        <v>253</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="T2">
+        <v>32564</v>
+      </c>
+      <c r="U2">
+        <v>70</v>
+      </c>
+      <c r="V2">
+        <v>54652</v>
+      </c>
+      <c r="W2" s="1">
+        <v>46069</v>
+      </c>
+      <c r="X2" t="s">
+        <v>563</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AB2">
+        <v>56464</v>
+      </c>
+      <c r="AC2">
+        <v>45</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>80</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>510</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>698</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46061</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>46069</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3883C6CD-3A6E-4057-B81E-312B0FC40198}">
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="29" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="22.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="K1" t="s">
+        <v>537</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="M1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46072</v>
       </c>
       <c r="D2" s="1">
-        <v>46027</v>
+        <v>46074</v>
       </c>
       <c r="E2" t="s">
-        <v>848</v>
+        <v>1177</v>
       </c>
       <c r="F2">
-        <v>23564</v>
-      </c>
-      <c r="G2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46054</v>
+        <v>29451</v>
+      </c>
+      <c r="G2">
+        <v>500</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2">
+        <v>987654331</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46072</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="N2" t="s">
+        <v>275</v>
+      </c>
+      <c r="O2">
+        <v>600</v>
+      </c>
+      <c r="P2">
+        <v>77777745</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>253</v>
+      </c>
+      <c r="R2" t="s">
+        <v>254</v>
+      </c>
+      <c r="S2">
+        <v>52413</v>
+      </c>
+      <c r="T2">
+        <v>700</v>
+      </c>
+      <c r="U2">
+        <v>52635</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="W2" t="s">
+        <v>563</v>
+      </c>
+      <c r="X2">
+        <v>526424</v>
+      </c>
+      <c r="Y2">
+        <v>800</v>
+      </c>
+      <c r="Z2">
+        <v>256412</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>46072</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AD2">
+        <v>900</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="AF2">
+        <v>123456</v>
+      </c>
+      <c r="AG2">
+        <v>52416</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -10899,29 +12287,249 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B73523-0C7D-4155-AC44-E87812CD37B8}">
-  <dimension ref="A1:B2"/>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1F95AA-9032-47A7-9B12-71766439ACDD}">
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="23.85546875" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="28" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>900</v>
       </c>
       <c r="B1" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>800</v>
+        <v>908</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D2">
+        <v>29451</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>52642</v>
+      </c>
+      <c r="J2" s="1">
+        <v>46073</v>
+      </c>
+      <c r="K2" t="s">
+        <v>246</v>
+      </c>
+      <c r="L2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2">
+        <v>55</v>
+      </c>
+      <c r="N2">
+        <v>56234</v>
+      </c>
+      <c r="O2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Q2">
+        <v>6958</v>
+      </c>
+      <c r="R2">
+        <v>100</v>
+      </c>
+      <c r="S2">
+        <v>56421</v>
+      </c>
+      <c r="T2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="V2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="W2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="Y2">
+        <v>60</v>
+      </c>
+      <c r="Z2">
+        <v>524126</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>46073</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>70</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AF2">
+        <v>25145</v>
+      </c>
+      <c r="AG2">
+        <v>5241</v>
+      </c>
+      <c r="AH2">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -10987,6 +12595,642 @@
       </c>
       <c r="G2" t="s">
         <v>725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD618DE6-3AFD-4017-B22F-08C9D50DAA49}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2">
+        <v>29452</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46072</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46074</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E58E864-6E8A-4FF7-945A-7E806EFB2D6C}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D1" t="s">
+        <v>532</v>
+      </c>
+      <c r="E1" t="s">
+        <v>533</v>
+      </c>
+      <c r="F1" t="s">
+        <v>535</v>
+      </c>
+      <c r="G1" t="s">
+        <v>536</v>
+      </c>
+      <c r="H1" t="s">
+        <v>901</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>546</v>
+      </c>
+      <c r="H2" t="s">
+        <v>908</v>
+      </c>
+      <c r="I2">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AA7E-88E2-4256-86EA-52919803DDCC}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46075</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1A5E74-AAFE-4352-879F-C9ADB66D4324}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46076</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46076</v>
+      </c>
+      <c r="E2">
+        <v>500</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46077</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="L2">
+        <v>29448</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A989A04-A33E-4EEF-912B-E0583A70A2FD}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>958</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D2">
+        <v>29459</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H2">
+        <v>1000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F09270-1FEE-4D7E-A2B1-067B6E58EC0B}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D1" t="s">
+        <v>976</v>
+      </c>
+      <c r="E1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F1" t="s">
+        <v>952</v>
+      </c>
+      <c r="G1" t="s">
+        <v>978</v>
+      </c>
+      <c r="H1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46055</v>
+      </c>
+      <c r="E2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F2">
+        <v>29344</v>
+      </c>
+      <c r="G2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46025</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B73523-0C7D-4155-AC44-E87812CD37B8}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>975</v>
+      </c>
+      <c r="C1" t="s">
+        <v>994</v>
+      </c>
+      <c r="D1" t="s">
+        <v>995</v>
+      </c>
+      <c r="E1" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C2" t="s">
+        <v>815</v>
+      </c>
+      <c r="D2" t="s">
+        <v>998</v>
+      </c>
+      <c r="E2" t="s">
+        <v>997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6946A-E358-4DE2-B43D-AD5F7808634C}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C1" t="s">
+        <v>920</v>
+      </c>
+      <c r="D1" t="s">
+        <v>982</v>
+      </c>
+      <c r="E1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F1" t="s">
+        <v>977</v>
+      </c>
+      <c r="G1" t="s">
+        <v>952</v>
+      </c>
+      <c r="H1" t="s">
+        <v>978</v>
+      </c>
+      <c r="I1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>981</v>
+      </c>
+      <c r="C2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F2" t="s">
+        <v>848</v>
+      </c>
+      <c r="G2">
+        <v>29344</v>
+      </c>
+      <c r="H2" t="s">
+        <v>910</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753D503-B7CA-43F7-BD19-60134A1E726F}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>980</v>
+      </c>
+      <c r="C1" t="s">
+        <v>921</v>
+      </c>
+      <c r="D1" t="s">
+        <v>976</v>
+      </c>
+      <c r="E1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F1" t="s">
+        <v>952</v>
+      </c>
+      <c r="G1" t="s">
+        <v>978</v>
+      </c>
+      <c r="H1" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>983</v>
+      </c>
+      <c r="C2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F2">
+        <v>23564</v>
+      </c>
+      <c r="G2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46054</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3836967F-B75E-4526-88FA-92217ED66D6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F89F56-BFD0-4A00-8DF7-5066F60F8CFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="71" activeTab="73" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="76" activeTab="78" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -81,11 +81,13 @@
     <sheet name="OP_Deposit_Transfer_Ip" sheetId="94" r:id="rId71"/>
     <sheet name="IP_Cheque_In_HandDetails" sheetId="95" r:id="rId72"/>
     <sheet name="IP_Cheque_In_Hand" sheetId="96" r:id="rId73"/>
-    <sheet name="Package_Duration_Modifiction" sheetId="97" r:id="rId74"/>
-    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId75"/>
-    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId76"/>
-    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId77"/>
-    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId78"/>
+    <sheet name="Package_Modifiction_Patient_Pag" sheetId="98" r:id="rId74"/>
+    <sheet name="ADT_Package_Multiple" sheetId="99" r:id="rId75"/>
+    <sheet name="Package_Duration_Modifiction" sheetId="97" r:id="rId76"/>
+    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId77"/>
+    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId78"/>
+    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId79"/>
+    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId80"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="1208">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -2847,9 +2849,6 @@
     <t>Asutosh</t>
   </si>
   <si>
-    <t>Asutosh_</t>
-  </si>
-  <si>
     <t>Enter_Add_Remaks</t>
   </si>
   <si>
@@ -3195,9 +3194,6 @@
     <t>PUNB0854</t>
   </si>
   <si>
-    <t>Fibroscan Scheme</t>
-  </si>
-  <si>
     <t>BADR ALL SHEMA</t>
   </si>
   <si>
@@ -3273,15 +3269,9 @@
     <t>1</t>
   </si>
   <si>
-    <t>GENERAL WARD (SEVENTH FLOOR)</t>
-  </si>
-  <si>
     <t>Alloted_bed_type_drp</t>
   </si>
   <si>
-    <t>ICU</t>
-  </si>
-  <si>
     <t>Enter_Bill_Number</t>
   </si>
   <si>
@@ -3688,6 +3678,51 @@
   </si>
   <si>
     <t>Himanshu Sharma Cardiologist</t>
+  </si>
+  <si>
+    <t>From_Date_Find_Patint_Pop</t>
+  </si>
+  <si>
+    <t>To_Date_Find_Patint_Pop</t>
+  </si>
+  <si>
+    <t>ADT_Station_Drp</t>
+  </si>
+  <si>
+    <t>ADT_Speciality_Drp</t>
+  </si>
+  <si>
+    <t>ADT_Doctor_Drp</t>
+  </si>
+  <si>
+    <t>Department_Drp</t>
+  </si>
+  <si>
+    <t>Search_Package_Name</t>
+  </si>
+  <si>
+    <t>Enter_Package_Alias_Name</t>
+  </si>
+  <si>
+    <t>AnupS</t>
+  </si>
+  <si>
+    <t>HIMANSHU WARD (AUTOMATION)</t>
+  </si>
+  <si>
+    <t>Search_First_Name</t>
+  </si>
+  <si>
+    <t>Adhoc</t>
+  </si>
+  <si>
+    <t>GENERAL SURGERY</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Hari</t>
   </si>
 </sst>
 </file>
@@ -8467,15 +8502,17 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F9016A-938F-4400-83E8-235BA46C870F}">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>768</v>
       </c>
@@ -8486,70 +8523,73 @@
         <v>770</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>771</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>776</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>777</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>779</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>780</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>781</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="Q1" s="8" t="s">
-        <v>1059</v>
-      </c>
       <c r="R1" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="S1" s="8" t="s">
         <v>783</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>784</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>785</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>786</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="W1" s="8" t="s">
         <v>787</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -8560,66 +8600,69 @@
         <v>5</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>33725</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>916</v>
-      </c>
       <c r="G2" s="9" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>792</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="I2" s="9" t="s">
         <v>793</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="9" t="s">
         <v>794</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="K2" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="L2" s="10" t="s">
         <v>795</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="M2" s="9" t="s">
         <v>796</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="N2" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="O2" s="11" t="s">
+      <c r="O2" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="P2" s="11" t="s">
         <v>798</v>
       </c>
-      <c r="P2" s="11" t="s">
-        <v>799</v>
-      </c>
       <c r="Q2" s="11" t="s">
-        <v>1060</v>
+        <v>828</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>1058</v>
+        <v>828</v>
       </c>
       <c r="S2" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="T2" s="11" t="s">
         <v>796</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="U2" s="11" t="s">
+      <c r="V2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="11" t="s">
+      <c r="W2" s="11" t="s">
         <v>915</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>801</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>801</v>
       </c>
     </row>
@@ -10463,10 +10506,10 @@
         <v>907</v>
       </c>
       <c r="K1" t="s">
+        <v>916</v>
+      </c>
+      <c r="L1" t="s">
         <v>917</v>
-      </c>
-      <c r="L1" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10501,7 +10544,7 @@
         <v>914</v>
       </c>
       <c r="K2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L2" t="s">
         <v>914</v>
@@ -10539,31 +10582,31 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1" t="s">
         <v>920</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>921</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>922</v>
-      </c>
-      <c r="F1" t="s">
-        <v>923</v>
       </c>
       <c r="G1" t="s">
         <v>450</v>
       </c>
       <c r="H1" t="s">
+        <v>923</v>
+      </c>
+      <c r="I1" t="s">
         <v>924</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>925</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>926</v>
-      </c>
-      <c r="K1" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -10574,10 +10617,10 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E2" s="1">
         <v>46032</v>
@@ -10589,10 +10632,10 @@
         <v>24137</v>
       </c>
       <c r="H2" t="s">
+        <v>929</v>
+      </c>
+      <c r="I2" t="s">
         <v>930</v>
-      </c>
-      <c r="I2" t="s">
-        <v>931</v>
       </c>
       <c r="J2" t="s">
         <v>523</v>
@@ -10635,7 +10678,7 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D1" t="s">
         <v>450</v>
@@ -10647,40 +10690,40 @@
         <v>423</v>
       </c>
       <c r="G1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1" t="s">
+        <v>933</v>
+      </c>
+      <c r="I1" t="s">
         <v>934</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>935</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>936</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>937</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>938</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>939</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>940</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>941</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>942</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>943</v>
-      </c>
-      <c r="R1" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -10691,7 +10734,7 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D2">
         <v>27510</v>
@@ -10706,22 +10749,22 @@
         <v>9876543210</v>
       </c>
       <c r="H2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="I2" t="s">
+        <v>944</v>
+      </c>
+      <c r="J2" t="s">
         <v>945</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>946</v>
-      </c>
-      <c r="K2" t="s">
-        <v>947</v>
       </c>
       <c r="L2" t="s">
         <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="N2">
         <v>100</v>
@@ -10895,19 +10938,19 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>950</v>
+      </c>
+      <c r="D1" t="s">
         <v>951</v>
       </c>
-      <c r="D1" t="s">
-        <v>952</v>
-      </c>
       <c r="E1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F1" t="s">
+        <v>955</v>
+      </c>
+      <c r="G1" t="s">
         <v>956</v>
-      </c>
-      <c r="G1" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -10918,13 +10961,13 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D2">
         <v>24722</v>
       </c>
       <c r="E2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
@@ -10967,13 +11010,13 @@
         <v>423</v>
       </c>
       <c r="E1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1" t="s">
         <v>450</v>
@@ -10996,10 +11039,10 @@
         <v>98766543210</v>
       </c>
       <c r="F2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2">
         <v>24722</v>
@@ -11034,13 +11077,13 @@
         <v>481</v>
       </c>
       <c r="D1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E1" t="s">
+        <v>958</v>
+      </c>
+      <c r="F1" t="s">
         <v>959</v>
-      </c>
-      <c r="F1" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -11051,7 +11094,7 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D2">
         <v>29336</v>
@@ -11098,43 +11141,43 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D1" t="s">
         <v>64</v>
       </c>
       <c r="E1" t="s">
+        <v>962</v>
+      </c>
+      <c r="F1" t="s">
+        <v>965</v>
+      </c>
+      <c r="G1" t="s">
         <v>963</v>
       </c>
-      <c r="F1" t="s">
-        <v>966</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>964</v>
-      </c>
-      <c r="H1" t="s">
-        <v>965</v>
       </c>
       <c r="I1" t="s">
         <v>604</v>
       </c>
       <c r="J1" t="s">
+        <v>970</v>
+      </c>
+      <c r="K1" t="s">
         <v>971</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>972</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>973</v>
       </c>
-      <c r="M1" t="s">
-        <v>974</v>
-      </c>
       <c r="N1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="O1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -11148,22 +11191,22 @@
         <v>28870</v>
       </c>
       <c r="D2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E2" t="s">
         <v>219</v>
       </c>
       <c r="F2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="J2" s="1">
         <v>46024</v>
@@ -11181,7 +11224,7 @@
         <v>9876543210</v>
       </c>
       <c r="O2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
   </sheetData>
@@ -11224,34 +11267,34 @@
         <v>423</v>
       </c>
       <c r="E1" t="s">
+        <v>983</v>
+      </c>
+      <c r="F1" t="s">
         <v>984</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>951</v>
+      </c>
+      <c r="H1" t="s">
         <v>985</v>
       </c>
-      <c r="G1" t="s">
-        <v>952</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>986</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>987</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>988</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>989</v>
       </c>
-      <c r="L1" t="s">
-        <v>990</v>
-      </c>
       <c r="M1" t="s">
+        <v>991</v>
+      </c>
+      <c r="N1" t="s">
         <v>992</v>
-      </c>
-      <c r="N1" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -11271,7 +11314,7 @@
         <v>9876543210</v>
       </c>
       <c r="F2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G2">
         <v>29296</v>
@@ -11289,7 +11332,7 @@
         <v>219</v>
       </c>
       <c r="L2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="M2" s="1">
         <v>46058</v>
@@ -11377,31 +11420,31 @@
         <v>423</v>
       </c>
       <c r="E1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F1" t="s">
-        <v>934</v>
+        <v>1203</v>
       </c>
       <c r="G1" t="s">
         <v>10</v>
       </c>
       <c r="H1" t="s">
+        <v>999</v>
+      </c>
+      <c r="I1" t="s">
         <v>1000</v>
       </c>
-      <c r="I1" t="s">
-        <v>1001</v>
-      </c>
       <c r="J1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="L1" t="s">
         <v>1003</v>
       </c>
-      <c r="K1" t="s">
-        <v>1003</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1004</v>
-      </c>
       <c r="M1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N1" t="s">
         <v>424</v>
@@ -11410,49 +11453,49 @@
         <v>751</v>
       </c>
       <c r="P1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q1" t="s">
         <v>1008</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1009</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1010</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1011</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1012</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1013</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1014</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1015</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1016</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1017</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1018</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1019</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>1020</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>1021</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>1022</v>
       </c>
       <c r="AE1" t="s">
         <v>71</v>
@@ -11461,40 +11504,40 @@
         <v>43</v>
       </c>
       <c r="AG1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="AH1" t="s">
         <v>1023</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>1024</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>1025</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>1026</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>1027</v>
       </c>
-      <c r="AL1" t="s">
-        <v>1028</v>
-      </c>
       <c r="AM1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="AN1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AO1" t="s">
         <v>1036</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>1038</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>1040</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>1042</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>1044</v>
       </c>
       <c r="AS1" t="s">
         <v>537</v>
@@ -11506,28 +11549,28 @@
         <v>242</v>
       </c>
       <c r="AV1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AX1" t="s">
         <v>1045</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>1046</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>1047</v>
       </c>
-      <c r="AY1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>1049</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>1051</v>
       </c>
-      <c r="BB1" t="s">
-        <v>1053</v>
-      </c>
       <c r="BC1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.25">
@@ -11547,13 +11590,13 @@
         <v>9876543210</v>
       </c>
       <c r="F2" t="s">
-        <v>933</v>
+        <v>712</v>
       </c>
       <c r="G2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I2">
         <v>29387</v>
@@ -11562,10 +11605,10 @@
         <v>815</v>
       </c>
       <c r="K2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L2" t="s">
         <v>1005</v>
-      </c>
-      <c r="L2" t="s">
-        <v>1006</v>
       </c>
       <c r="M2" t="s">
         <v>214</v>
@@ -11598,10 +11641,10 @@
         <v>46063</v>
       </c>
       <c r="W2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="X2" t="s">
         <v>1029</v>
-      </c>
-      <c r="X2" t="s">
-        <v>1030</v>
       </c>
       <c r="Y2">
         <v>2000</v>
@@ -11613,22 +11656,22 @@
         <v>963852741</v>
       </c>
       <c r="AB2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="AC2" t="s">
         <v>8</v>
       </c>
       <c r="AD2">
-        <v>741852963</v>
+        <v>1232963</v>
       </c>
       <c r="AE2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AG2" t="s">
         <v>1032</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>1034</v>
       </c>
       <c r="AH2">
         <v>6000</v>
@@ -11637,7 +11680,7 @@
         <v>5</v>
       </c>
       <c r="AJ2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="AK2" t="s">
         <v>16</v>
@@ -11652,13 +11695,13 @@
         <v>46063</v>
       </c>
       <c r="AO2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AP2" t="s">
         <v>1039</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>1041</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>1043</v>
       </c>
       <c r="AR2" t="s">
         <v>15</v>
@@ -11685,16 +11728,16 @@
         <v>500</v>
       </c>
       <c r="AZ2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="BA2" t="s">
         <v>1050</v>
       </c>
-      <c r="BA2" t="s">
-        <v>1052</v>
-      </c>
       <c r="BB2" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="BC2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
   </sheetData>
@@ -11781,19 +11824,19 @@
         <v>450</v>
       </c>
       <c r="D1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G1" t="s">
         <v>1061</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>1062</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1066</v>
       </c>
       <c r="I1" t="s">
         <v>242</v>
@@ -11802,10 +11845,10 @@
         <v>499</v>
       </c>
       <c r="K1" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="L1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="M1" t="s">
         <v>501</v>
@@ -11814,85 +11857,85 @@
         <v>557</v>
       </c>
       <c r="O1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="R1" t="s">
         <v>1068</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>1069</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="U1" t="s">
         <v>1071</v>
       </c>
-      <c r="R1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="AF1" t="s">
         <v>1073</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AG1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AH1" t="s">
         <v>1074</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AI1" t="s">
         <v>1075</v>
       </c>
-      <c r="V1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>1091</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>1092</v>
-      </c>
-      <c r="AD1" t="s">
+      <c r="AJ1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AK1" t="s">
         <v>1093</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AL1" t="s">
         <v>1094</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>1097</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>1098</v>
       </c>
       <c r="AM1" t="s">
         <v>424</v>
       </c>
       <c r="AN1" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="AO1" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
@@ -11906,7 +11949,7 @@
         <v>29402</v>
       </c>
       <c r="D2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E2">
         <v>50</v>
@@ -11933,7 +11976,7 @@
         <v>3216549787</v>
       </c>
       <c r="M2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="N2" t="s">
         <v>246</v>
@@ -11951,7 +11994,7 @@
         <v>253</v>
       </c>
       <c r="S2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="T2">
         <v>32564</v>
@@ -11969,13 +12012,13 @@
         <v>563</v>
       </c>
       <c r="Y2" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="Z2">
         <v>10</v>
       </c>
       <c r="AA2" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="AB2">
         <v>56464</v>
@@ -11984,7 +12027,7 @@
         <v>45</v>
       </c>
       <c r="AD2" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="AE2">
         <v>55</v>
@@ -11996,22 +12039,22 @@
         <v>510</v>
       </c>
       <c r="AH2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="AI2" t="s">
         <v>698</v>
       </c>
       <c r="AJ2" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="AK2" t="s">
         <v>15</v>
       </c>
       <c r="AL2" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="AM2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="AN2" s="1">
         <v>46061</v>
@@ -12076,103 +12119,103 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D1" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="E1" t="s">
         <v>481</v>
       </c>
       <c r="F1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G1" t="s">
         <v>532</v>
       </c>
       <c r="H1" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="I1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="J1" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="K1" t="s">
         <v>537</v>
       </c>
       <c r="L1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="M1" t="s">
         <v>242</v>
       </c>
       <c r="N1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="R1" t="s">
         <v>1107</v>
       </c>
-      <c r="O1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="T1" t="s">
         <v>1109</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>1110</v>
       </c>
-      <c r="R1" t="s">
+      <c r="V1" t="s">
         <v>1111</v>
       </c>
-      <c r="S1" t="s">
+      <c r="W1" t="s">
         <v>1112</v>
       </c>
-      <c r="T1" t="s">
+      <c r="X1" t="s">
         <v>1113</v>
       </c>
-      <c r="U1" t="s">
+      <c r="Y1" t="s">
         <v>1114</v>
       </c>
-      <c r="V1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>1116</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>1117</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AC1" t="s">
         <v>1118</v>
       </c>
-      <c r="Z1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="AE1" t="s">
         <v>1121</v>
       </c>
-      <c r="AB1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>1122</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>1123</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AI1" t="s">
         <v>1125</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.25">
@@ -12189,7 +12232,7 @@
         <v>46074</v>
       </c>
       <c r="E2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="F2">
         <v>29451</v>
@@ -12198,7 +12241,7 @@
         <v>500</v>
       </c>
       <c r="H2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
@@ -12213,7 +12256,7 @@
         <v>46072</v>
       </c>
       <c r="M2" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="N2" t="s">
         <v>275</v>
@@ -12240,7 +12283,7 @@
         <v>52635</v>
       </c>
       <c r="V2" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="W2" t="s">
         <v>563</v>
@@ -12258,16 +12301,16 @@
         <v>46072</v>
       </c>
       <c r="AB2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="AC2" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="AD2">
         <v>900</v>
       </c>
       <c r="AE2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="AF2">
         <v>123456</v>
@@ -12276,7 +12319,7 @@
         <v>52416</v>
       </c>
       <c r="AH2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="AI2">
         <v>1000</v>
@@ -12335,97 +12378,97 @@
         <v>481</v>
       </c>
       <c r="D1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="E1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H1" t="s">
         <v>1132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>1133</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>1134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L1" t="s">
         <v>1136</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>1137</v>
       </c>
-      <c r="J1" t="s">
+      <c r="N1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="S1" t="s">
         <v>1138</v>
       </c>
-      <c r="K1" t="s">
+      <c r="T1" t="s">
         <v>1139</v>
       </c>
-      <c r="L1" t="s">
+      <c r="U1" t="s">
         <v>1140</v>
       </c>
-      <c r="M1" t="s">
+      <c r="V1" t="s">
         <v>1141</v>
       </c>
-      <c r="N1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="W1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Z1" t="s">
         <v>1152</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="AA1" t="s">
         <v>1153</v>
       </c>
-      <c r="R1" t="s">
+      <c r="AB1" t="s">
         <v>1154</v>
       </c>
-      <c r="S1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="V1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="W1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AD1" t="s">
         <v>1156</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AE1" t="s">
         <v>1157</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AF1" t="s">
         <v>1158</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AG1" t="s">
         <v>1159</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AH1" t="s">
         <v>1160</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
@@ -12436,7 +12479,7 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="D2">
         <v>29451</v>
@@ -12448,7 +12491,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -12475,7 +12518,7 @@
         <v>253</v>
       </c>
       <c r="P2" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="Q2">
         <v>6958</v>
@@ -12490,16 +12533,16 @@
         <v>15</v>
       </c>
       <c r="U2" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="V2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="W2" t="s">
         <v>8</v>
       </c>
       <c r="X2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="Y2">
         <v>60</v>
@@ -12511,7 +12554,7 @@
         <v>46073</v>
       </c>
       <c r="AB2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="AC2" t="s">
         <v>8</v>
@@ -12520,7 +12563,7 @@
         <v>70</v>
       </c>
       <c r="AE2" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="AF2">
         <v>25145</v>
@@ -12623,13 +12666,13 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="D1" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="E1" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="F1" t="s">
         <v>570</v>
@@ -12646,7 +12689,7 @@
         <v>29452</v>
       </c>
       <c r="D2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="E2" s="1">
         <v>46072</v>
@@ -12678,7 +12721,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="B1" t="s">
         <v>19</v>
@@ -12702,7 +12745,7 @@
         <v>901</v>
       </c>
       <c r="I1" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -12710,16 +12753,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C2" t="s">
         <v>1173</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1177</v>
       </c>
       <c r="D2">
         <v>500</v>
       </c>
       <c r="E2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -12759,10 +12802,10 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="D1" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -12812,34 +12855,34 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G1" t="s">
         <v>1180</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>1181</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>1182</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>1183</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1186</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1187</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -12865,16 +12908,16 @@
         <v>46077</v>
       </c>
       <c r="H2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="K2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="L2">
         <v>29448</v>
@@ -12886,6 +12929,121 @@
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54354EAF-1340-4149-90BD-A72ECC03E494}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D2">
+        <v>29454</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46078</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46078</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECF30F3-2043-4C80-AFAE-88161DDB3A16}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A989A04-A33E-4EEF-912B-E0583A70A2FD}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12909,25 +13067,25 @@
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F1" t="s">
         <v>1189</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="I1" t="s">
         <v>1191</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -12938,13 +13096,13 @@
         <v>908</v>
       </c>
       <c r="C2" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D2">
         <v>29459</v>
       </c>
       <c r="E2" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="F2">
         <v>50</v>
@@ -12956,7 +13114,7 @@
         <v>1000</v>
       </c>
       <c r="I2" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
     </row>
   </sheetData>
@@ -12964,13 +13122,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F09270-1FEE-4D7E-A2B1-067B6E58EC0B}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
@@ -12984,25 +13142,25 @@
         <v>900</v>
       </c>
       <c r="B1" t="s">
+        <v>974</v>
+      </c>
+      <c r="C1" t="s">
+        <v>920</v>
+      </c>
+      <c r="D1" t="s">
         <v>975</v>
       </c>
-      <c r="C1" t="s">
-        <v>921</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>976</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>951</v>
+      </c>
+      <c r="G1" t="s">
         <v>977</v>
       </c>
-      <c r="F1" t="s">
-        <v>952</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>978</v>
-      </c>
-      <c r="H1" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -13010,7 +13168,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1058</v>
+        <v>1202</v>
       </c>
       <c r="C2" t="s">
         <v>523</v>
@@ -13036,13 +13194,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B73523-0C7D-4155-AC44-E87812CD37B8}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
@@ -13053,16 +13211,16 @@
         <v>900</v>
       </c>
       <c r="B1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C1" t="s">
+        <v>993</v>
+      </c>
+      <c r="D1" t="s">
         <v>994</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>995</v>
-      </c>
-      <c r="E1" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -13070,16 +13228,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1058</v>
+        <v>1202</v>
       </c>
       <c r="C2" t="s">
         <v>815</v>
       </c>
       <c r="D2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
   </sheetData>
@@ -13087,7 +13245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6946A-E358-4DE2-B43D-AD5F7808634C}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13108,28 +13266,28 @@
         <v>900</v>
       </c>
       <c r="B1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="C1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E1" t="s">
+        <v>975</v>
+      </c>
+      <c r="F1" t="s">
         <v>976</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>951</v>
+      </c>
+      <c r="H1" t="s">
         <v>977</v>
       </c>
-      <c r="G1" t="s">
-        <v>952</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>978</v>
-      </c>
-      <c r="I1" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -13137,7 +13295,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="C2" t="s">
         <v>523</v>
@@ -13159,78 +13317,6 @@
       </c>
       <c r="I2" s="1">
         <v>46057</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753D503-B7CA-43F7-BD19-60134A1E726F}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1" t="s">
-        <v>980</v>
-      </c>
-      <c r="C1" t="s">
-        <v>921</v>
-      </c>
-      <c r="D1" t="s">
-        <v>976</v>
-      </c>
-      <c r="E1" t="s">
-        <v>977</v>
-      </c>
-      <c r="F1" t="s">
-        <v>952</v>
-      </c>
-      <c r="G1" t="s">
-        <v>978</v>
-      </c>
-      <c r="H1" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D2" s="1">
-        <v>46027</v>
-      </c>
-      <c r="E2" t="s">
-        <v>848</v>
-      </c>
-      <c r="F2">
-        <v>23564</v>
-      </c>
-      <c r="G2" t="s">
-        <v>523</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46054</v>
       </c>
     </row>
   </sheetData>
@@ -13310,6 +13396,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753D503-B7CA-43F7-BD19-60134A1E726F}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1" t="s">
+        <v>920</v>
+      </c>
+      <c r="D1" t="s">
+        <v>975</v>
+      </c>
+      <c r="E1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F1" t="s">
+        <v>951</v>
+      </c>
+      <c r="G1" t="s">
+        <v>977</v>
+      </c>
+      <c r="H1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46027</v>
+      </c>
+      <c r="E2" t="s">
+        <v>848</v>
+      </c>
+      <c r="F2">
+        <v>23564</v>
+      </c>
+      <c r="G2" t="s">
+        <v>523</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544200DA-9307-4890-A10B-977B5EEE653D}">
   <dimension ref="A1:B2"/>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F89F56-BFD0-4A00-8DF7-5066F60F8CFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35034639-C629-4E93-A2EA-638DA06F7B4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="76" activeTab="78" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="83" activeTab="85" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -88,6 +88,12 @@
     <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId78"/>
     <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId79"/>
     <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId80"/>
+    <sheet name="ER_Registration_Page" sheetId="100" r:id="rId81"/>
+    <sheet name="ER_To_Admit_Sheet" sheetId="101" r:id="rId82"/>
+    <sheet name="Er_Activity_Sheet" sheetId="102" r:id="rId83"/>
+    <sheet name="Er_Admission_Update_DateTime" sheetId="103" r:id="rId84"/>
+    <sheet name="Er_Admission_Surgery_Request" sheetId="104" r:id="rId85"/>
+    <sheet name="Er_CreditLimitPage" sheetId="105" r:id="rId86"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -99,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2138" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="1348">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -3723,6 +3729,426 @@
   </si>
   <si>
     <t>Hari</t>
+  </si>
+  <si>
+    <t>Facility_Dropdwon</t>
+  </si>
+  <si>
+    <t>Station_Dropdwon</t>
+  </si>
+  <si>
+    <t>Gender_drp</t>
+  </si>
+  <si>
+    <t>Age_Text</t>
+  </si>
+  <si>
+    <t>age_type_drp</t>
+  </si>
+  <si>
+    <t>Email_Id</t>
+  </si>
+  <si>
+    <t>Patient_Condition_text</t>
+  </si>
+  <si>
+    <t>Kin_Relationship</t>
+  </si>
+  <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
+    <t>Year(s)</t>
+  </si>
+  <si>
+    <t>Triage Level 1</t>
+  </si>
+  <si>
+    <t>Emergency</t>
+  </si>
+  <si>
+    <t>First_Name</t>
+  </si>
+  <si>
+    <t>Middle_Name</t>
+  </si>
+  <si>
+    <t>Last_Name</t>
+  </si>
+  <si>
+    <t>Father_Name</t>
+  </si>
+  <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>Spouse_Name</t>
+  </si>
+  <si>
+    <t>Hii</t>
+  </si>
+  <si>
+    <t>City_Town_Drp</t>
+  </si>
+  <si>
+    <t>Locality_po_Drp</t>
+  </si>
+  <si>
+    <t>Other_Locality</t>
+  </si>
+  <si>
+    <t>Enter_Pin_Number</t>
+  </si>
+  <si>
+    <t>Preferred_Language_Drp</t>
+  </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <t>PrimarySpeciality_Drp</t>
+  </si>
+  <si>
+    <t>Emergency Services</t>
+  </si>
+  <si>
+    <t>Primary_ConsultantDrp</t>
+  </si>
+  <si>
+    <t>Employee296</t>
+  </si>
+  <si>
+    <t>Enter_Referred_By</t>
+  </si>
+  <si>
+    <t>Enter_Abc_Text</t>
+  </si>
+  <si>
+    <t>Stay_Duration_Value</t>
+  </si>
+  <si>
+    <t>Phone_Number</t>
+  </si>
+  <si>
+    <t>Education_Drp</t>
+  </si>
+  <si>
+    <t>Bachleors</t>
+  </si>
+  <si>
+    <t>Mother_Name_Text</t>
+  </si>
+  <si>
+    <t>Parwati</t>
+  </si>
+  <si>
+    <t>Id_Type_Drp</t>
+  </si>
+  <si>
+    <t>Id_Number</t>
+  </si>
+  <si>
+    <t>Id_Card_Type_Drp_Pop</t>
+  </si>
+  <si>
+    <t>PASSPORT NUMBER</t>
+  </si>
+  <si>
+    <t>National_Id_Text</t>
+  </si>
+  <si>
+    <t>Co_Speciality_Drp</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Co_Consultant_Drp</t>
+  </si>
+  <si>
+    <t>Blood_Group_Drp</t>
+  </si>
+  <si>
+    <t>A (-ve)</t>
+  </si>
+  <si>
+    <t>Source_Drp</t>
+  </si>
+  <si>
+    <t>Sub_Source_Drp</t>
+  </si>
+  <si>
+    <t>Ward_Drp</t>
+  </si>
+  <si>
+    <t>EMERGENCY OPD(GROUND FLOOR)</t>
+  </si>
+  <si>
+    <t>Admission_Type_drp</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Triage_Drp</t>
+  </si>
+  <si>
+    <t>Infectious_Patient_Drp</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Enter_Patient_Links</t>
+  </si>
+  <si>
+    <t>abcdef</t>
+  </si>
+  <si>
+    <t>Hidden</t>
+  </si>
+  <si>
+    <t>Kushal</t>
+  </si>
+  <si>
+    <t>Automaion</t>
+  </si>
+  <si>
+    <t>Fibroscan Scheme</t>
+  </si>
+  <si>
+    <t>AuthClaim_No</t>
+  </si>
+  <si>
+    <t>Standard_Deductible_No</t>
+  </si>
+  <si>
+    <t>Standrad_Co_pay_No</t>
+  </si>
+  <si>
+    <t>Letter_No</t>
+  </si>
+  <si>
+    <t>Leter_Date</t>
+  </si>
+  <si>
+    <t>Auth_Amount_No</t>
+  </si>
+  <si>
+    <t>Employee_Issued_By</t>
+  </si>
+  <si>
+    <t>Permanent_Address</t>
+  </si>
+  <si>
+    <t>Permanent_City_Drp</t>
+  </si>
+  <si>
+    <t>Permanent_Locolity_Drp</t>
+  </si>
+  <si>
+    <t>Blanks_Name</t>
+  </si>
+  <si>
+    <t>Permanent_Phone_No</t>
+  </si>
+  <si>
+    <t>Permanent_Mobile_No</t>
+  </si>
+  <si>
+    <t>Abhanpur</t>
+  </si>
+  <si>
+    <t>shahabad</t>
+  </si>
+  <si>
+    <t>MLC_Number</t>
+  </si>
+  <si>
+    <t>MLC_Type_Drp</t>
+  </si>
+  <si>
+    <t>Injury_Type_Drp</t>
+  </si>
+  <si>
+    <t>BroughtBy_Text</t>
+  </si>
+  <si>
+    <t>MLC_Transport_Drp</t>
+  </si>
+  <si>
+    <t>Place_Of_Accident</t>
+  </si>
+  <si>
+    <t>MLC_Police_Station</t>
+  </si>
+  <si>
+    <t>Anup_</t>
+  </si>
+  <si>
+    <t>Assault including Domestic</t>
+  </si>
+  <si>
+    <t>Grievance injury</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>MLC_Officer_Name</t>
+  </si>
+  <si>
+    <t>MLC_Officer_Phone</t>
+  </si>
+  <si>
+    <t>MLC_Complaint_No</t>
+  </si>
+  <si>
+    <t>Injury_Date</t>
+  </si>
+  <si>
+    <t>Initiation_Date</t>
+  </si>
+  <si>
+    <t>MLC_Cause_Accident</t>
+  </si>
+  <si>
+    <t>Identification_Marks</t>
+  </si>
+  <si>
+    <t>Remaks</t>
+  </si>
+  <si>
+    <t>Xyz</t>
+  </si>
+  <si>
+    <t>Pqr</t>
+  </si>
+  <si>
+    <t>Buckle_Police</t>
+  </si>
+  <si>
+    <t>Kin_Name</t>
+  </si>
+  <si>
+    <t>Kin_Phone_No</t>
+  </si>
+  <si>
+    <t>Kin_Mobile_No</t>
+  </si>
+  <si>
+    <t>Driver_Name</t>
+  </si>
+  <si>
+    <t>Mobile_Driver</t>
+  </si>
+  <si>
+    <t>Ambulance_No</t>
+  </si>
+  <si>
+    <t>Ambulanc_Othetr_Details</t>
+  </si>
+  <si>
+    <t>Shiv Sankar</t>
+  </si>
+  <si>
+    <t>DEUS1245</t>
+  </si>
+  <si>
+    <t>Ambulanc Othetr Details Test</t>
+  </si>
+  <si>
+    <t>Shama</t>
+  </si>
+  <si>
+    <t>Requested_Bed_Type_Drp</t>
+  </si>
+  <si>
+    <t>Allotted_Bed_Type_Drp</t>
+  </si>
+  <si>
+    <t>Ambulance</t>
+  </si>
+  <si>
+    <t>Mode_Of_Transport</t>
+  </si>
+  <si>
+    <t>Primary_Speciality_Drp</t>
+  </si>
+  <si>
+    <t>Primary_Consultant_Drp</t>
+  </si>
+  <si>
+    <t>Secondary_Speciality_Drp</t>
+  </si>
+  <si>
+    <t>Secondary_Consultant_Drp</t>
+  </si>
+  <si>
+    <t>Dummy Doctor</t>
+  </si>
+  <si>
+    <t>Bobby Lord</t>
+  </si>
+  <si>
+    <t>Next_Kin_Address</t>
+  </si>
+  <si>
+    <t>Emergency_Contacts_Name</t>
+  </si>
+  <si>
+    <t>Emergency_Contacts_Phone</t>
+  </si>
+  <si>
+    <t>Billing_Counselling</t>
+  </si>
+  <si>
+    <t>Clinical_Counselling</t>
+  </si>
+  <si>
+    <t>Billing XYZ</t>
+  </si>
+  <si>
+    <t>Clinical PQR</t>
+  </si>
+  <si>
+    <t>Excel_Enter_UHID</t>
+  </si>
+  <si>
+    <t>Enter_Er_Number</t>
+  </si>
+  <si>
+    <t>Patient_From_Date</t>
+  </si>
+  <si>
+    <t>Patient_To_Date</t>
+  </si>
+  <si>
+    <t>Service_Name_Drp</t>
+  </si>
+  <si>
+    <t>SPSL.886284</t>
+  </si>
+  <si>
+    <t>19-03-20206</t>
+  </si>
+  <si>
+    <t>select</t>
+  </si>
+  <si>
+    <t>Request_Type_Drp</t>
+  </si>
+  <si>
+    <t>Surgery Request Only</t>
+  </si>
+  <si>
+    <t>Enter_Er_No</t>
+  </si>
+  <si>
+    <t>Enter_New_Credit_Limit</t>
+  </si>
+  <si>
+    <t>SPSL.886289</t>
   </si>
 </sst>
 </file>
@@ -13468,6 +13894,988 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9984DF16-1A75-4635-9101-206351EE1444}">
+  <dimension ref="A1:CP2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="41" width="22" customWidth="1"/>
+    <col min="42" max="42" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="46" width="22" customWidth="1"/>
+    <col min="47" max="47" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="62" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="20" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="18.7109375" customWidth="1"/>
+    <col min="82" max="82" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="20" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="86" max="86" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="87" max="87" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="88" max="88" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="27.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="M1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N1" t="s">
+        <v>774</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>452</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:94" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F2" t="s">
+        <v>932</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>37883</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="M2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1216</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="P2" t="s">
+        <v>932</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="R2">
+        <v>12345</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="V2" t="s">
+        <v>6</v>
+      </c>
+      <c r="W2">
+        <v>5242521</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>963852</v>
+      </c>
+      <c r="Z2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="AD2">
+        <v>91</v>
+      </c>
+      <c r="AE2">
+        <v>8565421589</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>462</v>
+      </c>
+      <c r="AH2">
+        <v>5415</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>815</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>214</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>215</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>216</v>
+      </c>
+      <c r="AZ2">
+        <v>12345</v>
+      </c>
+      <c r="BA2">
+        <v>65432</v>
+      </c>
+      <c r="BB2">
+        <v>5</v>
+      </c>
+      <c r="BC2">
+        <v>2</v>
+      </c>
+      <c r="BD2">
+        <v>20</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>46098</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>698</v>
+      </c>
+      <c r="BG2">
+        <v>10</v>
+      </c>
+      <c r="BH2">
+        <v>3</v>
+      </c>
+      <c r="BI2">
+        <v>12</v>
+      </c>
+      <c r="BJ2">
+        <v>13</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>15</v>
+      </c>
+      <c r="BL2">
+        <v>1</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="BQ2">
+        <v>8574965412</v>
+      </c>
+      <c r="BR2">
+        <v>1236547890</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="BV2">
+        <v>4512</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>15</v>
+      </c>
+      <c r="CA2">
+        <v>8574129632</v>
+      </c>
+      <c r="CB2">
+        <v>24514</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>156</v>
+      </c>
+      <c r="CD2" s="1">
+        <v>46099</v>
+      </c>
+      <c r="CE2" s="1">
+        <v>46099</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>16</v>
+      </c>
+      <c r="CK2">
+        <v>8527419630</v>
+      </c>
+      <c r="CL2">
+        <v>2583697410</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="CN2">
+        <v>6352417890</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Z2" r:id="rId1" xr:uid="{65926C93-3127-4024-AD34-9DD98339EFEA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A30D36C-D939-4BE3-85F0-D947812190E5}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="I2" t="s">
+        <v>796</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2">
+        <v>8527419630</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6369E9D3-38E6-4C79-8ECA-0C7BD071C1A0}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D2">
+        <v>1508821</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2297FC27-8B95-4994-AC55-7579464FE13D}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8BE78D-628E-45AA-BF42-043C9973B432}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F1" t="s">
+        <v>690</v>
+      </c>
+      <c r="G1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46101</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D228C6F9-C725-4AFE-A2CE-EEC08172626E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D2">
+        <v>1508824</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544200DA-9307-4890-A10B-977B5EEE653D}">
   <dimension ref="A1:B2"/>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35034639-C629-4E93-A2EA-638DA06F7B4D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7C8F4C-FC34-408A-A54B-331799C6C444}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="83" activeTab="85" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="84" activeTab="86" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -94,6 +94,7 @@
     <sheet name="Er_Admission_Update_DateTime" sheetId="103" r:id="rId84"/>
     <sheet name="Er_Admission_Surgery_Request" sheetId="104" r:id="rId85"/>
     <sheet name="Er_CreditLimitPage" sheetId="105" r:id="rId86"/>
+    <sheet name="Er_Billing_Page" sheetId="106" r:id="rId87"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -105,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2362" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="1352">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4149,6 +4150,18 @@
   </si>
   <si>
     <t>SPSL.886289</t>
+  </si>
+  <si>
+    <t>Search_Frome_Date</t>
+  </si>
+  <si>
+    <t>Search_To_Date</t>
+  </si>
+  <si>
+    <t>Punb47521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anup </t>
   </si>
 </sst>
 </file>
@@ -14876,6 +14889,244 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F797D-41D1-4D94-B217-DDA96A6A7FB3}">
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H1" t="s">
+        <v>751</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="W1" t="s">
+        <v>752</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>994</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46100</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46104</v>
+      </c>
+      <c r="E2">
+        <v>1508826</v>
+      </c>
+      <c r="F2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" t="s">
+        <v>216</v>
+      </c>
+      <c r="I2">
+        <v>123</v>
+      </c>
+      <c r="J2">
+        <v>5241</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2" t="s">
+        <v>875</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>123456</v>
+      </c>
+      <c r="O2" s="1">
+        <v>46107</v>
+      </c>
+      <c r="P2">
+        <v>9876542</v>
+      </c>
+      <c r="Q2">
+        <v>524163</v>
+      </c>
+      <c r="R2">
+        <v>50</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>52416352</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="V2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" t="s">
+        <v>480</v>
+      </c>
+      <c r="X2" t="s">
+        <v>698</v>
+      </c>
+      <c r="Y2">
+        <v>10</v>
+      </c>
+      <c r="Z2">
+        <v>50</v>
+      </c>
+      <c r="AA2">
+        <v>12456</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>815</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>997</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544200DA-9307-4890-A10B-977B5EEE653D}">
   <dimension ref="A1:B2"/>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7C8F4C-FC34-408A-A54B-331799C6C444}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6DC503-D929-4993-97E2-6B4476A3E150}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="84" activeTab="86" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="92" activeTab="93" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -67,34 +67,41 @@
     <sheet name="IP_Billing_Audit_Clearance" sheetId="74" r:id="rId57"/>
     <sheet name="Acknowledge_Discharge_Page" sheetId="75" r:id="rId58"/>
     <sheet name="MiscellaneousCharges_Page" sheetId="76" r:id="rId59"/>
-    <sheet name="Ip_Ambulance_MrdCharges" sheetId="77" r:id="rId60"/>
-    <sheet name="IP_Pending_Investigation" sheetId="78" r:id="rId61"/>
-    <sheet name="IP_Credit_Limit" sheetId="79" r:id="rId62"/>
-    <sheet name="IP_General_OrderEntry" sheetId="80" r:id="rId63"/>
-    <sheet name="Ip_Doctor_Vist_Page" sheetId="86" r:id="rId64"/>
-    <sheet name="Ip_Billing_Page" sheetId="87" r:id="rId65"/>
-    <sheet name="Ip_Bill_Add_on_Bill" sheetId="89" r:id="rId66"/>
-    <sheet name="Due_Settlement_Page" sheetId="90" r:id="rId67"/>
-    <sheet name="Ip_DepositRefund_Page" sheetId="91" r:id="rId68"/>
-    <sheet name="Ip_Refund_Page" sheetId="92" r:id="rId69"/>
-    <sheet name="Ip_ReceiptUtility_Page" sheetId="93" r:id="rId70"/>
-    <sheet name="OP_Deposit_Transfer_Ip" sheetId="94" r:id="rId71"/>
-    <sheet name="IP_Cheque_In_HandDetails" sheetId="95" r:id="rId72"/>
-    <sheet name="IP_Cheque_In_Hand" sheetId="96" r:id="rId73"/>
-    <sheet name="Package_Modifiction_Patient_Pag" sheetId="98" r:id="rId74"/>
-    <sheet name="ADT_Package_Multiple" sheetId="99" r:id="rId75"/>
-    <sheet name="Package_Duration_Modifiction" sheetId="97" r:id="rId76"/>
-    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId77"/>
-    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId78"/>
-    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId79"/>
-    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId80"/>
-    <sheet name="ER_Registration_Page" sheetId="100" r:id="rId81"/>
-    <sheet name="ER_To_Admit_Sheet" sheetId="101" r:id="rId82"/>
-    <sheet name="Er_Activity_Sheet" sheetId="102" r:id="rId83"/>
-    <sheet name="Er_Admission_Update_DateTime" sheetId="103" r:id="rId84"/>
-    <sheet name="Er_Admission_Surgery_Request" sheetId="104" r:id="rId85"/>
-    <sheet name="Er_CreditLimitPage" sheetId="105" r:id="rId86"/>
-    <sheet name="Er_Billing_Page" sheetId="106" r:id="rId87"/>
+    <sheet name="Sheet1" sheetId="107" r:id="rId60"/>
+    <sheet name="Ip_Ambulance_MrdCharges" sheetId="77" r:id="rId61"/>
+    <sheet name="IP_Pending_Investigation" sheetId="78" r:id="rId62"/>
+    <sheet name="IP_Credit_Limit" sheetId="79" r:id="rId63"/>
+    <sheet name="IP_General_OrderEntry" sheetId="80" r:id="rId64"/>
+    <sheet name="Ip_Doctor_Vist_Page" sheetId="86" r:id="rId65"/>
+    <sheet name="Ip_Billing_Page" sheetId="87" r:id="rId66"/>
+    <sheet name="Ip_Bill_Add_on_Bill" sheetId="89" r:id="rId67"/>
+    <sheet name="Due_Settlement_Page" sheetId="90" r:id="rId68"/>
+    <sheet name="Ip_DepositRefund_Page" sheetId="91" r:id="rId69"/>
+    <sheet name="Ip_Refund_Page" sheetId="92" r:id="rId70"/>
+    <sheet name="Ip_ReceiptUtility_Page" sheetId="93" r:id="rId71"/>
+    <sheet name="OP_Deposit_Transfer_Ip" sheetId="94" r:id="rId72"/>
+    <sheet name="IP_Cheque_In_HandDetails" sheetId="95" r:id="rId73"/>
+    <sheet name="IP_Cheque_In_Hand" sheetId="96" r:id="rId74"/>
+    <sheet name="Package_Modifiction_Patient_Pag" sheetId="98" r:id="rId75"/>
+    <sheet name="ADT_Package_Multiple" sheetId="99" r:id="rId76"/>
+    <sheet name="Package_Duration_Modifiction" sheetId="97" r:id="rId77"/>
+    <sheet name="Nursing_Clearance_Page" sheetId="81" r:id="rId78"/>
+    <sheet name="Nursing_Activity_Page" sheetId="85" r:id="rId79"/>
+    <sheet name="Pharmacy_Discharge_Notification" sheetId="83" r:id="rId80"/>
+    <sheet name="Lab_Clearance_Page" sheetId="84" r:id="rId81"/>
+    <sheet name="ER_Registration_Page" sheetId="100" r:id="rId82"/>
+    <sheet name="ER_To_Admit_Sheet" sheetId="101" r:id="rId83"/>
+    <sheet name="Er_Activity_Sheet" sheetId="102" r:id="rId84"/>
+    <sheet name="Er_Admission_Update_DateTime" sheetId="103" r:id="rId85"/>
+    <sheet name="Er_Admission_Surgery_Request" sheetId="104" r:id="rId86"/>
+    <sheet name="Er_CreditLimitPage" sheetId="105" r:id="rId87"/>
+    <sheet name="Er_Billing_Page" sheetId="106" r:id="rId88"/>
+    <sheet name="Er_MiscellaneousCharges_Page" sheetId="108" r:id="rId89"/>
+    <sheet name="Er_AmbulanceCharges_Page" sheetId="109" r:id="rId90"/>
+    <sheet name="Er_TOC_Approval_Page" sheetId="110" r:id="rId91"/>
+    <sheet name="Er_Discharge_Notification_Page" sheetId="111" r:id="rId92"/>
+    <sheet name="Er_DueSettlement_Page" sheetId="113" r:id="rId93"/>
+    <sheet name="Er_DepositRefund_Page" sheetId="114" r:id="rId94"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2409" uniqueCount="1352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1380">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4162,6 +4169,90 @@
   </si>
   <si>
     <t xml:space="preserve">Anup </t>
+  </si>
+  <si>
+    <t>Amount_enter</t>
+  </si>
+  <si>
+    <t>Dr.Employee102</t>
+  </si>
+  <si>
+    <t>SPSL.886318</t>
+  </si>
+  <si>
+    <t>Name_Search_Medical_Record_Charges</t>
+  </si>
+  <si>
+    <t>Admission Fees</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>Search_TOC_Approved_From_Date</t>
+  </si>
+  <si>
+    <t>Search_TOC_Approved_To_Date</t>
+  </si>
+  <si>
+    <t>Cancel Remarks Bill</t>
+  </si>
+  <si>
+    <t>Cancel_Bill_Reamrks</t>
+  </si>
+  <si>
+    <t>Status_DropDwon</t>
+  </si>
+  <si>
+    <t>Patient_Type_Drp</t>
+  </si>
+  <si>
+    <t>Discharge</t>
+  </si>
+  <si>
+    <t>ER NO</t>
+  </si>
+  <si>
+    <t>Find_Patient_Frome_Date</t>
+  </si>
+  <si>
+    <t>Enter_Due_Amount_Er_Number</t>
+  </si>
+  <si>
+    <t>Enter_Rounding_Off_Settlement</t>
+  </si>
+  <si>
+    <t>Remarks_Due_Settlement</t>
+  </si>
+  <si>
+    <t>Anup Due Settlement</t>
+  </si>
+  <si>
+    <t>Enter_Cheque_Number</t>
+  </si>
+  <si>
+    <t>Less_Amount_Due_Amount</t>
+  </si>
+  <si>
+    <t>Serach_Company_Frome_Date</t>
+  </si>
+  <si>
+    <t>Serach_Company_To_Date</t>
+  </si>
+  <si>
+    <t>Deposit_Case_Amount</t>
+  </si>
+  <si>
+    <t>Deposit_Remarks</t>
+  </si>
+  <si>
+    <t>Relationship_Drp</t>
+  </si>
+  <si>
+    <t>Deposit_Cheque_Amount</t>
+  </si>
+  <si>
+    <t>Deposit_Er_Number</t>
   </si>
 </sst>
 </file>
@@ -4228,7 +4319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4242,6 +4333,7 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11356,6 +11448,15 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C888D81-EFB3-4567-80FC-3EBB12959E54}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{524359A0-2104-4284-80DF-E4D467856F6E}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11420,7 +11521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658E2525-34D4-493E-BC75-42FCB8785136}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11493,7 +11594,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D44066-CCF8-4E69-8974-47BB22EA7B20}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11550,7 +11651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D536C2E-2049-4378-975D-D0690C151CB0}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11671,7 +11772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869035F4-0440-4683-84DA-B1D3A25F3843}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11785,7 +11886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FB2B9F-5C63-4573-B0FF-F4AA329DC337}">
   <dimension ref="A1:BC2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12185,7 +12286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D418190-A307-409C-9B13-520CE3406CF2}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12208,7 +12309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EB81613-B25D-46A1-9C96-7C4B253B73B9}">
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12508,7 +12609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3883C6CD-3A6E-4057-B81E-312B0FC40198}">
   <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12769,7 +12870,72 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E25BFB-5A64-45CB-AFD0-C13AA2181D17}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>718</v>
+      </c>
+      <c r="D1" t="s">
+        <v>719</v>
+      </c>
+      <c r="E1" t="s">
+        <v>720</v>
+      </c>
+      <c r="F1" t="s">
+        <v>721</v>
+      </c>
+      <c r="G1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D2" t="s">
+        <v>723</v>
+      </c>
+      <c r="E2" t="s">
+        <v>724</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46043</v>
+      </c>
+      <c r="G2" t="s">
+        <v>725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1F95AA-9032-47A7-9B12-71766439ACDD}">
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13019,72 +13185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E25BFB-5A64-45CB-AFD0-C13AA2181D17}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>718</v>
-      </c>
-      <c r="D1" t="s">
-        <v>719</v>
-      </c>
-      <c r="E1" t="s">
-        <v>720</v>
-      </c>
-      <c r="F1" t="s">
-        <v>721</v>
-      </c>
-      <c r="G1" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D2" t="s">
-        <v>723</v>
-      </c>
-      <c r="E2" t="s">
-        <v>724</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46043</v>
-      </c>
-      <c r="G2" t="s">
-        <v>725</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD618DE6-3AFD-4017-B22F-08C9D50DAA49}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13142,7 +13243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E58E864-6E8A-4FF7-945A-7E806EFB2D6C}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13222,7 +13323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077AA7E-88E2-4256-86EA-52919803DDCC}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13267,7 +13368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A1A5E74-AAFE-4352-879F-C9ADB66D4324}">
   <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13367,7 +13468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54354EAF-1340-4149-90BD-A72ECC03E494}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13424,7 +13525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ECF30F3-2043-4C80-AFAE-88161DDB3A16}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13482,7 +13583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A989A04-A33E-4EEF-912B-E0583A70A2FD}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13561,7 +13662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12F09270-1FEE-4D7E-A2B1-067B6E58EC0B}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13633,7 +13734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B73523-0C7D-4155-AC44-E87812CD37B8}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13677,85 +13778,6 @@
       </c>
       <c r="E2" t="s">
         <v>996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6946A-E358-4DE2-B43D-AD5F7808634C}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1" t="s">
-        <v>979</v>
-      </c>
-      <c r="C1" t="s">
-        <v>919</v>
-      </c>
-      <c r="D1" t="s">
-        <v>981</v>
-      </c>
-      <c r="E1" t="s">
-        <v>975</v>
-      </c>
-      <c r="F1" t="s">
-        <v>976</v>
-      </c>
-      <c r="G1" t="s">
-        <v>951</v>
-      </c>
-      <c r="H1" t="s">
-        <v>977</v>
-      </c>
-      <c r="I1" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>980</v>
-      </c>
-      <c r="C2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E2" s="1">
-        <v>46054</v>
-      </c>
-      <c r="F2" t="s">
-        <v>848</v>
-      </c>
-      <c r="G2">
-        <v>29344</v>
-      </c>
-      <c r="H2" t="s">
-        <v>910</v>
-      </c>
-      <c r="I2" s="1">
-        <v>46057</v>
       </c>
     </row>
   </sheetData>
@@ -13836,6 +13858,85 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48C6946A-E358-4DE2-B43D-AD5F7808634C}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1" t="s">
+        <v>919</v>
+      </c>
+      <c r="D1" t="s">
+        <v>981</v>
+      </c>
+      <c r="E1" t="s">
+        <v>975</v>
+      </c>
+      <c r="F1" t="s">
+        <v>976</v>
+      </c>
+      <c r="G1" t="s">
+        <v>951</v>
+      </c>
+      <c r="H1" t="s">
+        <v>977</v>
+      </c>
+      <c r="I1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>980</v>
+      </c>
+      <c r="C2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F2" t="s">
+        <v>848</v>
+      </c>
+      <c r="G2">
+        <v>29344</v>
+      </c>
+      <c r="H2" t="s">
+        <v>910</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2753D503-B7CA-43F7-BD19-60134A1E726F}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13907,7 +14008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9984DF16-1A75-4635-9101-206351EE1444}">
   <dimension ref="A1:CP2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14561,7 +14662,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A30D36C-D939-4BE3-85F0-D947812190E5}">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14682,7 +14783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6369E9D3-38E6-4C79-8ECA-0C7BD071C1A0}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14745,7 +14846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2297FC27-8B95-4994-AC55-7579464FE13D}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14774,7 +14875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8BE78D-628E-45AA-BF42-043C9973B432}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14839,7 +14940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D228C6F9-C725-4AFE-A2CE-EEC08172626E}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14889,7 +14990,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F797D-41D1-4D94-B217-DDA96A6A7FB3}">
   <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15037,7 +15138,7 @@
         <v>46104</v>
       </c>
       <c r="E2">
-        <v>1508826</v>
+        <v>1508833</v>
       </c>
       <c r="F2" t="s">
         <v>214</v>
@@ -15124,6 +15225,99 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31373D41-CE00-4FCF-80C5-C80B936CA804}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>948</v>
+      </c>
+      <c r="D1" t="s">
+        <v>450</v>
+      </c>
+      <c r="E1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G1" t="s">
+        <v>935</v>
+      </c>
+      <c r="H1" t="s">
+        <v>936</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J1" t="s">
+        <v>940</v>
+      </c>
+      <c r="K1" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D2">
+        <v>1508832</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46003</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46108</v>
+      </c>
+      <c r="G2" t="s">
+        <v>945</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>400</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -15155,4 +15349,470 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E91BB5C-5E49-4DB9-9FB9-44F7CC387A01}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s">
+        <v>948</v>
+      </c>
+      <c r="F1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H1" t="s">
+        <v>956</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46101</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F2">
+        <v>1508832</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E09F33E-BC12-4F39-AE5B-A7CC7E51637E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2">
+        <v>1508837</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46111</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA2505F4-A146-4541-AE1A-D1742769B6EE}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D1" t="s">
+        <v>919</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46109</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46112</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="I2">
+        <v>1508804</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11B928DB-F65E-4332-B1DF-634D0E704CBC}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E1" t="s">
+        <v>424</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="J1" t="s">
+        <v>497</v>
+      </c>
+      <c r="K1" t="s">
+        <v>242</v>
+      </c>
+      <c r="L1" t="s">
+        <v>499</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46112</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46101</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="H2" s="13">
+        <v>1508851</v>
+      </c>
+      <c r="I2">
+        <v>123456</v>
+      </c>
+      <c r="J2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="13">
+        <v>10</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C0EE80-01C8-4453-A92B-89D25A36D783}">
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="K1" t="s">
+        <v>537</v>
+      </c>
+      <c r="L1" t="s">
+        <v>497</v>
+      </c>
+      <c r="M1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N1" t="s">
+        <v>499</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46111</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F2">
+        <v>1508844</v>
+      </c>
+      <c r="G2">
+        <v>700</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2">
+        <v>800</v>
+      </c>
+      <c r="K2">
+        <v>123456</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="N2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O2">
+        <v>1508832</v>
+      </c>
+      <c r="P2" s="1">
+        <v>46114</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6DC503-D929-4993-97E2-6B4476A3E150}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E1674-2346-4704-B66C-BF4CE2AB1B8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="92" activeTab="93" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="100" activeTab="102" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -101,7 +101,16 @@
     <sheet name="Er_TOC_Approval_Page" sheetId="110" r:id="rId91"/>
     <sheet name="Er_Discharge_Notification_Page" sheetId="111" r:id="rId92"/>
     <sheet name="Er_DueSettlement_Page" sheetId="113" r:id="rId93"/>
-    <sheet name="Er_DepositRefund_Page" sheetId="114" r:id="rId94"/>
+    <sheet name="Er_Deposit_Page" sheetId="114" r:id="rId94"/>
+    <sheet name="Er_Refund_Page" sheetId="115" r:id="rId95"/>
+    <sheet name="ER_Order_Page" sheetId="116" r:id="rId96"/>
+    <sheet name="Pharmacy_IpIssue_Page" sheetId="117" r:id="rId97"/>
+    <sheet name="Pharmacy_Retun_Page" sheetId="118" r:id="rId98"/>
+    <sheet name="Er_Sales_Consumption_Page" sheetId="119" r:id="rId99"/>
+    <sheet name="Er_Lab_Report_Page" sheetId="120" r:id="rId100"/>
+    <sheet name="Er_CancelEmergencyIssue_Page" sheetId="121" r:id="rId101"/>
+    <sheet name="Er_Raise_New_Request_Page" sheetId="122" r:id="rId102"/>
+    <sheet name="Er_Requisition_List_Page" sheetId="123" r:id="rId103"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -113,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2507" uniqueCount="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="1506">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4253,6 +4262,384 @@
   </si>
   <si>
     <t>Deposit_Er_Number</t>
+  </si>
+  <si>
+    <t>Deposit_Credit_Card_Number</t>
+  </si>
+  <si>
+    <t>Deposit_Credit_Card_Drp</t>
+  </si>
+  <si>
+    <t>Deposit_Bank_Name</t>
+  </si>
+  <si>
+    <t>Deposit_Credit_Card_Trans_No</t>
+  </si>
+  <si>
+    <t>Deposit_Credit_Card_Amount</t>
+  </si>
+  <si>
+    <t>Deposit_Credit_Card_Other_Details</t>
+  </si>
+  <si>
+    <t>NEFT_RTGS_Trans_No</t>
+  </si>
+  <si>
+    <t>NEFT_RTGS_Date</t>
+  </si>
+  <si>
+    <t>NEFT_RTGS_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>NEFT_RTGS_Branch_Name</t>
+  </si>
+  <si>
+    <t>NEFT_RTGS_Amount</t>
+  </si>
+  <si>
+    <t>Ernter_Refound_Amount</t>
+  </si>
+  <si>
+    <t>Refound_Payable_Name</t>
+  </si>
+  <si>
+    <t>Refound_Remarks</t>
+  </si>
+  <si>
+    <t>Refound Remarks</t>
+  </si>
+  <si>
+    <t>Refound_Cheque_Number</t>
+  </si>
+  <si>
+    <t>Refound_Cheque_Date</t>
+  </si>
+  <si>
+    <t>Refound_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>Refound_Cheque_Branch_Name</t>
+  </si>
+  <si>
+    <t>Refound_Cheque_Amount</t>
+  </si>
+  <si>
+    <t>Refound_Credit_Number</t>
+  </si>
+  <si>
+    <t>Refound_Card_Name_Drp</t>
+  </si>
+  <si>
+    <t>Refound_Credit_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>Refound_Trans_No</t>
+  </si>
+  <si>
+    <t>Refound_Amount_Credit_Card</t>
+  </si>
+  <si>
+    <t>NEFT_Account_No</t>
+  </si>
+  <si>
+    <t>NEFT_Accound_Holder_Name</t>
+  </si>
+  <si>
+    <t>NEFT_Account_Type</t>
+  </si>
+  <si>
+    <t>Saveing</t>
+  </si>
+  <si>
+    <t>NEFT_Bank_Name_Drp</t>
+  </si>
+  <si>
+    <t>BANK OF AMERICA</t>
+  </si>
+  <si>
+    <t>NEFT_IFSC_Code</t>
+  </si>
+  <si>
+    <t>PUNB52415</t>
+  </si>
+  <si>
+    <t>NEFT_RGTS_Finance_Amount</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Trans_No</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Trans_Date</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Banks_Name_Drp</t>
+  </si>
+  <si>
+    <t>NEFT_Processed_Amount</t>
+  </si>
+  <si>
+    <t>Refound_Other_Payment_Mode_Drp</t>
+  </si>
+  <si>
+    <t>Refound_Other_Transation_No</t>
+  </si>
+  <si>
+    <t>Refound_Other_Remarks</t>
+  </si>
+  <si>
+    <t>Refound_Other_Amount</t>
+  </si>
+  <si>
+    <t>BHARATQR</t>
+  </si>
+  <si>
+    <t>Deposit_Other_Payment_Mode_Drp</t>
+  </si>
+  <si>
+    <t>Deposit_Other_Transaction_Id</t>
+  </si>
+  <si>
+    <t>Deposit_Other_Remarks</t>
+  </si>
+  <si>
+    <t>Deposit_Other_Amount</t>
+  </si>
+  <si>
+    <t>Anup Deposit</t>
+  </si>
+  <si>
+    <t>ER No</t>
+  </si>
+  <si>
+    <t>Entetr_Pathology_Test</t>
+  </si>
+  <si>
+    <t>Priority_Drp</t>
+  </si>
+  <si>
+    <t>Select_Pathology_Sample_Drp</t>
+  </si>
+  <si>
+    <t>Fluid</t>
+  </si>
+  <si>
+    <t>abcd</t>
+  </si>
+  <si>
+    <t>Enter_No_Of_Times</t>
+  </si>
+  <si>
+    <t>Entetr_Other_Test</t>
+  </si>
+  <si>
+    <t>2d echo</t>
+  </si>
+  <si>
+    <t>Entetr_Profiles_Test</t>
+  </si>
+  <si>
+    <t>avin</t>
+  </si>
+  <si>
+    <t>Gen_Ordered_By_Drp</t>
+  </si>
+  <si>
+    <t>Search_By_Gen_Order_Items</t>
+  </si>
+  <si>
+    <t>Procedure Charges</t>
+  </si>
+  <si>
+    <t>Employee101</t>
+  </si>
+  <si>
+    <t>Dialysis</t>
+  </si>
+  <si>
+    <t>Remarks_Gen_Order</t>
+  </si>
+  <si>
+    <t>Anup Gen Order Remarks</t>
+  </si>
+  <si>
+    <t>Drug_Select_Store_Drp</t>
+  </si>
+  <si>
+    <t>Drug_Item_Code_Drp</t>
+  </si>
+  <si>
+    <t>Drug_Ordering_Doctor_Drp</t>
+  </si>
+  <si>
+    <t>Search_Box_Drug</t>
+  </si>
+  <si>
+    <t>Drug_Route_Drp</t>
+  </si>
+  <si>
+    <t>Drug_Frequency_Drp</t>
+  </si>
+  <si>
+    <t>Drug_Duration</t>
+  </si>
+  <si>
+    <t>Drug_Quantity</t>
+  </si>
+  <si>
+    <t>Drug_Priority</t>
+  </si>
+  <si>
+    <t>Drug_Remarks</t>
+  </si>
+  <si>
+    <t>Drug_UOM_Drp</t>
+  </si>
+  <si>
+    <t>Drug_Dose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENERAL </t>
+  </si>
+  <si>
+    <t>3 week</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>Drug_Interval_Drp</t>
+  </si>
+  <si>
+    <t>Stat</t>
+  </si>
+  <si>
+    <t>Anup Drug Order</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>00007-KAILASH</t>
+  </si>
+  <si>
+    <t>ANGIPLAT</t>
+  </si>
+  <si>
+    <t>Discharge_Remaks</t>
+  </si>
+  <si>
+    <t>Er Discharged</t>
+  </si>
+  <si>
+    <t>Select_Item_Code_Drp</t>
+  </si>
+  <si>
+    <t>Search_Drug_Sales_Consumables_Item</t>
+  </si>
+  <si>
+    <t>ACINOSTOP</t>
+  </si>
+  <si>
+    <t>&lt;-Select-&gt;</t>
+  </si>
+  <si>
+    <t>Item_Description_Quenty</t>
+  </si>
+  <si>
+    <t>Remarks_Sales</t>
+  </si>
+  <si>
+    <t>Print_From_Date</t>
+  </si>
+  <si>
+    <t>Print_To_Date</t>
+  </si>
+  <si>
+    <t>Report_Faclility_Drp</t>
+  </si>
+  <si>
+    <t>Fron_Date_Report</t>
+  </si>
+  <si>
+    <t>To_Date_Report</t>
+  </si>
+  <si>
+    <t>SPSL.886365</t>
+  </si>
+  <si>
+    <t>Enter_Retun_Durg_Quenty</t>
+  </si>
+  <si>
+    <t>Enter_From_Date</t>
+  </si>
+  <si>
+    <t>Enter_To_Date</t>
+  </si>
+  <si>
+    <t>Enter_Transfusion_Datetime</t>
+  </si>
+  <si>
+    <t>RH_Factor_Drp</t>
+  </si>
+  <si>
+    <t>PT_INR_Value_Sec</t>
+  </si>
+  <si>
+    <t>APTT_Value_Sec</t>
+  </si>
+  <si>
+    <t>Haemoglobin_Value</t>
+  </si>
+  <si>
+    <t>Platelet_Count_Value</t>
+  </si>
+  <si>
+    <t>Reason_Transfusion_Text</t>
+  </si>
+  <si>
+    <t>Reason_Transfusion_ClinicalDiagnosis_Text</t>
+  </si>
+  <si>
+    <t>Previous_Blood_Group_Drp</t>
+  </si>
+  <si>
+    <t>Previous_Rh_Factor_Drp</t>
+  </si>
+  <si>
+    <t>Reaction_Text</t>
+  </si>
+  <si>
+    <t>Women_Pregnancy</t>
+  </si>
+  <si>
+    <t>Request_Component_Drp</t>
+  </si>
+  <si>
+    <t>Request_List_Qty</t>
+  </si>
+  <si>
+    <t>Portable</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>NEGATIVE</t>
+  </si>
+  <si>
+    <t>Platelet</t>
+  </si>
+  <si>
+    <t>Enter_Frome_Date</t>
+  </si>
+  <si>
+    <t>Enter_UHID_Number</t>
+  </si>
+  <si>
+    <t>SPSL.884865</t>
   </si>
 </sst>
 </file>
@@ -5194,6 +5581,350 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C3A4FF-AFE5-49A0-BDD5-DE672B236BBD}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46113</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46127</v>
+      </c>
+      <c r="F2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB44F89-9345-4195-85EA-AFBA16B160BE}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2">
+        <v>1508875</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB872C2-C14B-4578-999A-6F355E1E9BDF}">
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="U1" t="s">
+        <v>604</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46122</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46128</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46128</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="I2">
+        <v>50</v>
+      </c>
+      <c r="J2">
+        <v>60</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2">
+        <v>70</v>
+      </c>
+      <c r="M2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="T2">
+        <v>5</v>
+      </c>
+      <c r="U2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V2">
+        <v>1508875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBF8748-A3A0-42BB-A394-FDBD5CA85BBE}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46128</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F2">
+        <v>29578</v>
+      </c>
+      <c r="G2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA277297-A5C9-4C74-A1D8-77D80FFE5D36}">
   <dimension ref="A1:BX2"/>
@@ -15683,7 +16414,7 @@
 
 <file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0C0EE80-01C8-4453-A92B-89D25A36D783}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -15703,9 +16434,24 @@
     <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="28" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="34" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>900</v>
       </c>
@@ -15757,8 +16503,53 @@
       <c r="Q1" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -15809,6 +16600,649 @@
       </c>
       <c r="Q2" s="1">
         <v>46115</v>
+      </c>
+      <c r="R2">
+        <v>99999</v>
+      </c>
+      <c r="S2" t="s">
+        <v>253</v>
+      </c>
+      <c r="T2" t="s">
+        <v>246</v>
+      </c>
+      <c r="U2">
+        <v>55555</v>
+      </c>
+      <c r="V2">
+        <v>600</v>
+      </c>
+      <c r="W2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X2">
+        <v>564245</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>46118</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB2">
+        <v>700</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AD2">
+        <v>35628</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AF2">
+        <v>800</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66691DF3-70F4-4DBD-8526-D6588FFBC7B9}">
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="19" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1508844</v>
+      </c>
+      <c r="B2">
+        <v>300</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E2">
+        <v>56421</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46119</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="I2">
+        <v>100</v>
+      </c>
+      <c r="J2">
+        <v>52462</v>
+      </c>
+      <c r="K2" t="s">
+        <v>562</v>
+      </c>
+      <c r="L2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M2">
+        <v>9658</v>
+      </c>
+      <c r="N2">
+        <v>50</v>
+      </c>
+      <c r="O2">
+        <v>7584001255</v>
+      </c>
+      <c r="P2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="U2">
+        <v>150</v>
+      </c>
+      <c r="V2">
+        <v>56428</v>
+      </c>
+      <c r="W2" s="1">
+        <v>46119</v>
+      </c>
+      <c r="X2" t="s">
+        <v>885</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>120</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AB2">
+        <v>63541</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD2">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59C7AC90-800A-43E1-8AAA-9841AF359BEF}">
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="L1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="S1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="U1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="V1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="X1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>993</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>994</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D2">
+        <v>1508875</v>
+      </c>
+      <c r="E2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="P2" t="s">
+        <v>980</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="R2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="U2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="V2">
+        <v>2</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="X2">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="AB2">
+        <v>5</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>815</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>997</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet97.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AB9BCB-16EB-4CD1-AA35-E202AEA32F8F}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>980</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet98.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463141A6-6B39-4D4C-84B8-2C696A78F9E3}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>980</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet99.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D893C1-D465-455D-AFEF-A18B2E34B542}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2">
+        <v>1508875</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>883</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46115</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46126</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E1674-2346-4704-B66C-BF4CE2AB1B8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EBC2DA-1A22-4014-9221-DBE34F656F9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="100" activeTab="102" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="104" activeTab="106" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -111,6 +111,10 @@
     <sheet name="Er_CancelEmergencyIssue_Page" sheetId="121" r:id="rId101"/>
     <sheet name="Er_Raise_New_Request_Page" sheetId="122" r:id="rId102"/>
     <sheet name="Er_Requisition_List_Page" sheetId="123" r:id="rId103"/>
+    <sheet name="Er_Issue_Drug_Acknowledgement" sheetId="124" r:id="rId104"/>
+    <sheet name="Er_Emergency_Clearance_Page" sheetId="125" r:id="rId105"/>
+    <sheet name="Er_Patient_Vitals" sheetId="126" r:id="rId106"/>
+    <sheet name="Er_IO_Chart_Page" sheetId="127" r:id="rId107"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -122,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2717" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1534">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4640,6 +4644,90 @@
   </si>
   <si>
     <t>SPSL.884865</t>
+  </si>
+  <si>
+    <t>Acknowled_Station_Drp</t>
+  </si>
+  <si>
+    <t>Enter_Bar_Code</t>
+  </si>
+  <si>
+    <t>ESD125</t>
+  </si>
+  <si>
+    <t>Emergency No</t>
+  </si>
+  <si>
+    <t>Check_Status_Drp</t>
+  </si>
+  <si>
+    <t>Acknowledged</t>
+  </si>
+  <si>
+    <t>Search_In_Mobile_Number</t>
+  </si>
+  <si>
+    <t>Search_In_Name</t>
+  </si>
+  <si>
+    <t>Add_Favorite_Vitals_Name</t>
+  </si>
+  <si>
+    <t>SPO2</t>
+  </si>
+  <si>
+    <t>Enter_ER_Number</t>
+  </si>
+  <si>
+    <t>Input_IV_Fluid_Drp</t>
+  </si>
+  <si>
+    <t>Input_Flow_Rate_Text</t>
+  </si>
+  <si>
+    <t>Input_Volume_Text</t>
+  </si>
+  <si>
+    <t>Input_Orl_Drp</t>
+  </si>
+  <si>
+    <t>Input_Quantity_Text</t>
+  </si>
+  <si>
+    <t>Input_Remarks</t>
+  </si>
+  <si>
+    <t>ASHLYTE-M 500ML AISHWARYA</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Anup Remarks Input</t>
+  </si>
+  <si>
+    <t>Output_Drp</t>
+  </si>
+  <si>
+    <t>Sub_Type_Drp</t>
+  </si>
+  <si>
+    <t>OutPut_Quantity_Text</t>
+  </si>
+  <si>
+    <t>Output_Remarks</t>
+  </si>
+  <si>
+    <t>Drainage</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>OutPut Remarks Anup</t>
   </si>
 </sst>
 </file>
@@ -5925,6 +6013,321 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33860EBB-607F-4BA7-9815-8609256A3FC8}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1" t="s">
+        <v>433</v>
+      </c>
+      <c r="G1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E2">
+        <v>1508888</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46129</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F014E74D-9720-4D1C-A566-0FD0C39BFA0F}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>920</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F1" t="s">
+        <v>925</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E2">
+        <v>1508836</v>
+      </c>
+      <c r="F2" t="s">
+        <v>523</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83725A67-9F43-48DC-862F-3B7649793BB4}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2">
+        <v>9876543210</v>
+      </c>
+      <c r="D2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F2">
+        <v>1508858</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159EF9B5-D009-4968-91C3-F6DD32306C5D}">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46091</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46136</v>
+      </c>
+      <c r="E2">
+        <v>1508858</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="O2">
+        <v>5</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA277297-A5C9-4C74-A1D8-77D80FFE5D36}">
   <dimension ref="A1:BX2"/>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EBC2DA-1A22-4014-9221-DBE34F656F9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACAA063-51CF-4956-AF1B-C08B350ABDB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="104" activeTab="106" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="109" activeTab="111" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -115,6 +115,11 @@
     <sheet name="Er_Emergency_Clearance_Page" sheetId="125" r:id="rId105"/>
     <sheet name="Er_Patient_Vitals" sheetId="126" r:id="rId106"/>
     <sheet name="Er_IO_Chart_Page" sheetId="127" r:id="rId107"/>
+    <sheet name="Endorsement_Tool" sheetId="128" r:id="rId108"/>
+    <sheet name="ER_Endorsement_Tool" sheetId="129" r:id="rId109"/>
+    <sheet name="Er_Pain_Assessment_Page" sheetId="130" r:id="rId110"/>
+    <sheet name="Er_Insertion_Monitering_Page" sheetId="131" r:id="rId111"/>
+    <sheet name="Er_Nurse_Care_Plan_Page" sheetId="132" r:id="rId112"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2776" uniqueCount="1534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="1610">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4728,6 +4733,234 @@
   </si>
   <si>
     <t>OutPut Remarks Anup</t>
+  </si>
+  <si>
+    <t>Shift</t>
+  </si>
+  <si>
+    <t>Diagnosis</t>
+  </si>
+  <si>
+    <t>AllergyRemarks</t>
+  </si>
+  <si>
+    <t>VitalName</t>
+  </si>
+  <si>
+    <t>LoginName</t>
+  </si>
+  <si>
+    <t>LoginPass</t>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Shift_Drp</t>
+  </si>
+  <si>
+    <t>Diagnosis_Text</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Allergy_Reaction_Drp</t>
+  </si>
+  <si>
+    <t>Enter_Since_Text</t>
+  </si>
+  <si>
+    <t>Since_Drp</t>
+  </si>
+  <si>
+    <t>Allergy_Remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CHORIONIC GONADOTROPHIN HP*</t>
+  </si>
+  <si>
+    <t>Agranulocytosis</t>
+  </si>
+  <si>
+    <t>week</t>
+  </si>
+  <si>
+    <t>Drug_Allergies_Value_Drp</t>
+  </si>
+  <si>
+    <t>Other_Allergies_Value_Drp</t>
+  </si>
+  <si>
+    <t>Food_Allergies_Value_Drp</t>
+  </si>
+  <si>
+    <t>aaaa</t>
+  </si>
+  <si>
+    <t>Flowers</t>
+  </si>
+  <si>
+    <t>Precipitating_Factor_Drp</t>
+  </si>
+  <si>
+    <t>Type_Of_Pain_Drp</t>
+  </si>
+  <si>
+    <t>Location_Drp</t>
+  </si>
+  <si>
+    <t>Pain_Score_Drp</t>
+  </si>
+  <si>
+    <t>Frequency_Drp</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Crushing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left Suprascapular </t>
+  </si>
+  <si>
+    <t>Intermittent</t>
+  </si>
+  <si>
+    <t>Muscle_Power_Grading_Drp</t>
+  </si>
+  <si>
+    <t>Sedation_Score_Drp</t>
+  </si>
+  <si>
+    <t>Nausea_Vomiting_Score_Drp</t>
+  </si>
+  <si>
+    <t>Duration_Text</t>
+  </si>
+  <si>
+    <t>Aggravating_Factors</t>
+  </si>
+  <si>
+    <t>Relieving_Factors</t>
+  </si>
+  <si>
+    <t>1 - Visible Contractions</t>
+  </si>
+  <si>
+    <t>1 - Arousable with Verbal stimuli</t>
+  </si>
+  <si>
+    <t>2 - Nausea&gt; 10 mins or vomiting twince</t>
+  </si>
+  <si>
+    <t>Location_Remarks</t>
+  </si>
+  <si>
+    <t>www</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>Post_Intervention_Score_Drp</t>
+  </si>
+  <si>
+    <t>Outcome_Text</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Intervention</t>
+  </si>
+  <si>
+    <t>Type_Of_Insertion_Drp</t>
+  </si>
+  <si>
+    <t>Site_Drp</t>
+  </si>
+  <si>
+    <t>Dressing_Drp</t>
+  </si>
+  <si>
+    <t>Central Venous Catheter</t>
+  </si>
+  <si>
+    <t>Internal Jugular Line</t>
+  </si>
+  <si>
+    <t>Easy Fix</t>
+  </si>
+  <si>
+    <t>Size_Text</t>
+  </si>
+  <si>
+    <t>No_Of_Attempts_Text</t>
+  </si>
+  <si>
+    <t>Insertion_Notes</t>
+  </si>
+  <si>
+    <t>Maintenance_Shift</t>
+  </si>
+  <si>
+    <t>Maintenance_Saline_Flush</t>
+  </si>
+  <si>
+    <t>Maintenance_VIP_Score</t>
+  </si>
+  <si>
+    <t>Maintenance_Genital_Meatal_Care</t>
+  </si>
+  <si>
+    <t>Night</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Maintenance Genital Meatal Care</t>
+  </si>
+  <si>
+    <t>Nursing_Assessment_Drp</t>
+  </si>
+  <si>
+    <t>Problem_Identified_Drp</t>
+  </si>
+  <si>
+    <t>Goal_Drp</t>
+  </si>
+  <si>
+    <t>Intervention_Drp</t>
+  </si>
+  <si>
+    <t>Implementation_Drp</t>
+  </si>
+  <si>
+    <t>Outcome_Drp</t>
+  </si>
+  <si>
+    <t>Special_Notes_Drp</t>
+  </si>
+  <si>
+    <t>Antenatal care plan</t>
+  </si>
+  <si>
+    <t>hemlata</t>
+  </si>
+  <si>
+    <t>Goal_2</t>
+  </si>
+  <si>
+    <t>Implement</t>
+  </si>
+  <si>
+    <t>DEMO</t>
   </si>
 </sst>
 </file>
@@ -4794,7 +5027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4809,6 +5042,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6328,6 +6566,171 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051423B8-38CC-4BC9-87F3-941DCB80A69C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>932</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{3DB8EA26-C4A6-4116-9B5A-B6825469ED02}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49BB8B6-1ADE-491A-A247-E07DA65E7FE6}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="43.5703125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1554</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="I2">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA277297-A5C9-4C74-A1D8-77D80FFE5D36}">
   <dimension ref="A1:BX2"/>
@@ -6872,6 +7275,332 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2484002-3E62-467F-8DB5-BEC1D6CB16AB}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="K1" t="s">
+        <v>604</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="R1" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ECFCE80-98A7-421A-9CA4-F96582E8F9FF}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H1" t="s">
+        <v>580</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1592</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>1586</v>
+      </c>
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+      <c r="M2" s="14" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F708D57E-D932-48CF-900D-A44E8A17C969}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>768</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>769</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10173,8 +10902,10 @@
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
@@ -10292,7 +11023,7 @@
         <v>795</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>796</v>
+        <v>1251</v>
       </c>
       <c r="N2" s="9" t="s">
         <v>378</v>
@@ -13909,7 +14640,7 @@
         <v>1173</v>
       </c>
       <c r="F2">
-        <v>29451</v>
+        <v>29855</v>
       </c>
       <c r="G2">
         <v>500</v>
@@ -14001,6 +14732,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14221,7 +14953,7 @@
         <v>1173</v>
       </c>
       <c r="D2">
-        <v>29451</v>
+        <v>29855</v>
       </c>
       <c r="E2">
         <v>50</v>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACAA063-51CF-4956-AF1B-C08B350ABDB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA2E10A-5C96-4922-8D1A-443751B0D922}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="109" activeTab="111" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="112" activeTab="115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -107,19 +107,23 @@
     <sheet name="Pharmacy_IpIssue_Page" sheetId="117" r:id="rId97"/>
     <sheet name="Pharmacy_Retun_Page" sheetId="118" r:id="rId98"/>
     <sheet name="Er_Sales_Consumption_Page" sheetId="119" r:id="rId99"/>
-    <sheet name="Er_Lab_Report_Page" sheetId="120" r:id="rId100"/>
-    <sheet name="Er_CancelEmergencyIssue_Page" sheetId="121" r:id="rId101"/>
-    <sheet name="Er_Raise_New_Request_Page" sheetId="122" r:id="rId102"/>
-    <sheet name="Er_Requisition_List_Page" sheetId="123" r:id="rId103"/>
-    <sheet name="Er_Issue_Drug_Acknowledgement" sheetId="124" r:id="rId104"/>
-    <sheet name="Er_Emergency_Clearance_Page" sheetId="125" r:id="rId105"/>
-    <sheet name="Er_Patient_Vitals" sheetId="126" r:id="rId106"/>
-    <sheet name="Er_IO_Chart_Page" sheetId="127" r:id="rId107"/>
-    <sheet name="Endorsement_Tool" sheetId="128" r:id="rId108"/>
-    <sheet name="ER_Endorsement_Tool" sheetId="129" r:id="rId109"/>
-    <sheet name="Er_Pain_Assessment_Page" sheetId="130" r:id="rId110"/>
-    <sheet name="Er_Insertion_Monitering_Page" sheetId="131" r:id="rId111"/>
-    <sheet name="Er_Nurse_Care_Plan_Page" sheetId="132" r:id="rId112"/>
+    <sheet name="Sheet5" sheetId="136" r:id="rId100"/>
+    <sheet name="Er_Lab_Report_Page" sheetId="120" r:id="rId101"/>
+    <sheet name="Er_CancelEmergencyIssue_Page" sheetId="121" r:id="rId102"/>
+    <sheet name="Er_Raise_New_Request_Page" sheetId="122" r:id="rId103"/>
+    <sheet name="Er_Requisition_List_Page" sheetId="123" r:id="rId104"/>
+    <sheet name="Er_Issue_Drug_Acknowledgement" sheetId="124" r:id="rId105"/>
+    <sheet name="Er_Emergency_Clearance_Page" sheetId="125" r:id="rId106"/>
+    <sheet name="Er_Patient_Vitals" sheetId="126" r:id="rId107"/>
+    <sheet name="Er_IO_Chart_Page" sheetId="127" r:id="rId108"/>
+    <sheet name="Endorsement_Tool" sheetId="128" r:id="rId109"/>
+    <sheet name="ER_Endorsement_Tool" sheetId="129" r:id="rId110"/>
+    <sheet name="Er_Pain_Assessment_Page" sheetId="130" r:id="rId111"/>
+    <sheet name="Er_Insertion_Monitering_Page" sheetId="131" r:id="rId112"/>
+    <sheet name="Er_Nurse_Care_Plan_Page" sheetId="132" r:id="rId113"/>
+    <sheet name="Er_Doctor_Notes_Page" sheetId="134" r:id="rId114"/>
+    <sheet name="Er_MAR_Page" sheetId="135" r:id="rId115"/>
+    <sheet name="Er_Missed Dose_Page" sheetId="137" r:id="rId116"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -131,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="1641">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4507,12 +4511,6 @@
     <t>Drug_Dose</t>
   </si>
   <si>
-    <t xml:space="preserve">GENERAL </t>
-  </si>
-  <si>
-    <t>3 week</t>
-  </si>
-  <si>
     <t>day</t>
   </si>
   <si>
@@ -4531,9 +4529,6 @@
     <t>00007-KAILASH</t>
   </si>
   <si>
-    <t>ANGIPLAT</t>
-  </si>
-  <si>
     <t>Discharge_Remaks</t>
   </si>
   <si>
@@ -4961,6 +4956,108 @@
   </si>
   <si>
     <t>DEMO</t>
+  </si>
+  <si>
+    <t>Preoperative_Doctor_Drp</t>
+  </si>
+  <si>
+    <t>Observations_Text</t>
+  </si>
+  <si>
+    <t>Preoperative Observations Notes</t>
+  </si>
+  <si>
+    <t>Doctor_Refral_Speciality_Drp</t>
+  </si>
+  <si>
+    <t>Doctor_Refral_Doctor_Drp</t>
+  </si>
+  <si>
+    <t>Doctor_Referral_Priority_Drp</t>
+  </si>
+  <si>
+    <t>Select_Notes_Style_Drp</t>
+  </si>
+  <si>
+    <t>pr</t>
+  </si>
+  <si>
+    <t>Dr.Bobby Lord</t>
+  </si>
+  <si>
+    <t>Doctor_Referral_Reason_Text</t>
+  </si>
+  <si>
+    <t>Hello_</t>
+  </si>
+  <si>
+    <t>New template for trend</t>
+  </si>
+  <si>
+    <t>Operative_Template_Drp</t>
+  </si>
+  <si>
+    <t>Pre_OT_Template_Drp</t>
+  </si>
+  <si>
+    <t>Doctor_PreAnaesthesia_Checkup_OPD</t>
+  </si>
+  <si>
+    <t>Physican_Template_Drp</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CT Consent Form</t>
+  </si>
+  <si>
+    <t>Dashboard_Facility_Drp</t>
+  </si>
+  <si>
+    <t>ORAL</t>
+  </si>
+  <si>
+    <t>Administer_Now_Reason_Remarks_Drp</t>
+  </si>
+  <si>
+    <t>Administer_Now_Remarks</t>
+  </si>
+  <si>
+    <t>Drug not received</t>
+  </si>
+  <si>
+    <t>Change_Schedule_Reason</t>
+  </si>
+  <si>
+    <t>Change_Schedule_Remarks</t>
+  </si>
+  <si>
+    <t>Patient is out</t>
+  </si>
+  <si>
+    <t>Anup Change Schedule</t>
+  </si>
+  <si>
+    <t>Unable_Administer_Reason_Drp</t>
+  </si>
+  <si>
+    <t>Unable_Administer_Remarks</t>
+  </si>
+  <si>
+    <t>Unable to Administer Remarks</t>
+  </si>
+  <si>
+    <t>ASHU_DOLO_650 CLINICAL NAME</t>
+  </si>
+  <si>
+    <t>BD.</t>
+  </si>
+  <si>
+    <t>Missed_Dose_Reason_Drp</t>
+  </si>
+  <si>
+    <t>Missed_Dose_Remarks</t>
+  </si>
+  <si>
+    <t>Missed Dose Remarks</t>
   </si>
 </sst>
 </file>
@@ -5908,6 +6005,15 @@
 </file>
 
 <file path=xl/worksheets/sheet100.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D86C55B-3509-451E-B36C-83A9F629E908}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3C3A4FF-AFE5-49A0-BDD5-DE672B236BBD}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5923,19 +6029,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1477</v>
+        <v>1474</v>
       </c>
       <c r="D1" t="s">
-        <v>1478</v>
+        <v>1475</v>
       </c>
       <c r="E1" t="s">
-        <v>1479</v>
+        <v>1476</v>
       </c>
       <c r="F1" t="s">
         <v>1257</v>
@@ -5964,7 +6070,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1480</v>
+        <v>1477</v>
       </c>
     </row>
   </sheetData>
@@ -5972,7 +6078,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet101.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BB44F89-9345-4195-85EA-AFBA16B160BE}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5985,7 +6091,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -5994,7 +6100,7 @@
         <v>1345</v>
       </c>
       <c r="D1" t="s">
-        <v>1481</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6016,7 +6122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet102.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB872C2-C14B-4578-999A-6F355E1E9BDF}">
   <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6047,19 +6153,19 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1482</v>
+        <v>1479</v>
       </c>
       <c r="D1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="E1" t="s">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="F1" t="s">
         <v>1430</v>
@@ -6068,43 +6174,43 @@
         <v>1253</v>
       </c>
       <c r="H1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="K1" t="s">
         <v>1485</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>1486</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>1487</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>1488</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>1489</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>1490</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>1491</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>1492</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>1493</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>1494</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1495</v>
-      </c>
-      <c r="S1" t="s">
-        <v>1496</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1497</v>
       </c>
       <c r="U1" t="s">
         <v>604</v>
@@ -6130,13 +6236,13 @@
         <v>46128</v>
       </c>
       <c r="F2" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="G2" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="H2" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="I2">
         <v>50</v>
@@ -6157,10 +6263,10 @@
         <v>15</v>
       </c>
       <c r="O2" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="P2" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="Q2" t="s">
         <v>15</v>
@@ -6169,7 +6275,7 @@
         <v>1224</v>
       </c>
       <c r="S2" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="T2">
         <v>5</v>
@@ -6186,7 +6292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet103.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBF8748-A3A0-42BB-A394-FDBD5CA85BBE}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6202,19 +6308,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="D1" t="s">
-        <v>1483</v>
+        <v>1480</v>
       </c>
       <c r="E1" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="F1" t="s">
         <v>1336</v>
@@ -6237,7 +6343,7 @@
         <v>46128</v>
       </c>
       <c r="E2" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="F2">
         <v>29578</v>
@@ -6251,7 +6357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet104.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33860EBB-607F-4BA7-9815-8609256A3FC8}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6266,16 +6372,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="D1" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="E1" t="s">
         <v>1336</v>
@@ -6298,7 +6404,7 @@
         <v>1258</v>
       </c>
       <c r="D2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="E2">
         <v>1508888</v>
@@ -6316,7 +6422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet105.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F014E74D-9720-4D1C-A566-0FD0C39BFA0F}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6332,7 +6438,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -6350,7 +6456,7 @@
         <v>925</v>
       </c>
       <c r="G1" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6364,7 +6470,7 @@
         <v>927</v>
       </c>
       <c r="D2" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="E2">
         <v>1508836</v>
@@ -6373,7 +6479,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
     </row>
   </sheetData>
@@ -6381,7 +6487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet106.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83725A67-9F43-48DC-862F-3B7649793BB4}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6396,22 +6502,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
       <c r="D1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F1" t="s">
         <v>1513</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6428,7 +6534,7 @@
         <v>712</v>
       </c>
       <c r="E2" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
       <c r="F2">
         <v>1508858</v>
@@ -6439,7 +6545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet107.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{159EF9B5-D009-4968-91C3-F6DD32306C5D}">
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6462,10 +6568,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="14" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
@@ -6478,44 +6584,44 @@
         <v>1336</v>
       </c>
       <c r="F1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="I1" t="s">
         <v>1517</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="K1" t="s">
         <v>1518</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>1519</v>
       </c>
-      <c r="I1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1521</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1522</v>
-      </c>
       <c r="M1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="P1" t="s">
         <v>1527</v>
       </c>
-      <c r="N1" t="s">
-        <v>1528</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1529</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1530</v>
-      </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="14" t="s">
         <v>1258</v>
       </c>
       <c r="C2" s="1">
@@ -6528,7 +6634,7 @@
         <v>1508858</v>
       </c>
       <c r="F2" t="s">
-        <v>1523</v>
+        <v>1520</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -6537,28 +6643,28 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="J2" t="s">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="K2">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1526</v>
+        <v>1523</v>
       </c>
       <c r="M2" t="s">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="N2" t="s">
-        <v>1532</v>
+        <v>1529</v>
       </c>
       <c r="O2">
         <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>1533</v>
+        <v>1530</v>
       </c>
     </row>
   </sheetData>
@@ -6566,7 +6672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet108.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051423B8-38CC-4BC9-87F3-941DCB80A69C}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6588,22 +6694,22 @@
         <v>769</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1533</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1534</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>1535</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>1536</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>1538</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>1539</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6614,7 +6720,7 @@
         <v>1202</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1540</v>
+        <v>1537</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>932</v>
@@ -6623,7 +6729,7 @@
         <v>932</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1541</v>
+        <v>1538</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>234</v>
@@ -6636,97 +6742,6 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{3DB8EA26-C4A6-4116-9B5A-B6825469ED02}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet109.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49BB8B6-1ADE-491A-A247-E07DA65E7FE6}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="43.5703125" style="14" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>769</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1543</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>1554</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>1553</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1545</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1546</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1547</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1351</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1549</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>1555</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>1556</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1550</v>
-      </c>
-      <c r="I2">
-        <v>45</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1551</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1351</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7279,6 +7294,97 @@
 </file>
 
 <file path=xl/worksheets/sheet110.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E49BB8B6-1ADE-491A-A247-E07DA65E7FE6}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="43.5703125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1550</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="I2">
+        <v>45</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2484002-3E62-467F-8DB5-BEC1D6CB16AB}">
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7304,58 +7410,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>768</v>
+        <v>1624</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>769</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F1" t="s">
         <v>1557</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>1558</v>
       </c>
-      <c r="E1" t="s">
-        <v>1559</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1560</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1561</v>
-      </c>
       <c r="H1" t="s">
-        <v>1566</v>
+        <v>1563</v>
       </c>
       <c r="I1" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="J1" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="K1" t="s">
         <v>604</v>
       </c>
       <c r="L1" t="s">
-        <v>1569</v>
+        <v>1566</v>
       </c>
       <c r="M1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="P1" t="s">
         <v>1575</v>
       </c>
-      <c r="N1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1571</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1578</v>
-      </c>
       <c r="Q1" t="s">
-        <v>1578</v>
+        <v>1575</v>
       </c>
       <c r="R1" t="s">
-        <v>1579</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -7366,28 +7472,28 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1562</v>
+        <v>1559</v>
       </c>
       <c r="D2" t="s">
-        <v>1563</v>
+        <v>1560</v>
       </c>
       <c r="E2" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="H2" t="s">
-        <v>1572</v>
+        <v>1569</v>
       </c>
       <c r="I2" t="s">
-        <v>1573</v>
+        <v>1570</v>
       </c>
       <c r="J2" t="s">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
@@ -7399,19 +7505,19 @@
         <v>8</v>
       </c>
       <c r="N2" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="O2" t="s">
-        <v>1577</v>
+        <v>1574</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>1581</v>
+        <v>1578</v>
       </c>
       <c r="R2" t="s">
-        <v>1580</v>
+        <v>1577</v>
       </c>
     </row>
   </sheetData>
@@ -7419,7 +7525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet111.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ECFCE80-98A7-421A-9CA4-F96582E8F9FF}">
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7441,43 +7547,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>768</v>
+        <v>1624</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>769</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1582</v>
+        <v>1579</v>
       </c>
       <c r="D1" t="s">
-        <v>1584</v>
+        <v>1581</v>
       </c>
       <c r="E1" t="s">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="F1" t="s">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="G1" t="s">
-        <v>1589</v>
+        <v>1586</v>
       </c>
       <c r="H1" t="s">
         <v>580</v>
       </c>
       <c r="I1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="L1" t="s">
         <v>1590</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>1591</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1592</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1593</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -7488,13 +7594,13 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1585</v>
+        <v>1582</v>
       </c>
       <c r="D2" t="s">
-        <v>1587</v>
+        <v>1584</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>1586</v>
+        <v>1583</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7509,16 +7615,16 @@
         <v>1351</v>
       </c>
       <c r="J2" t="s">
-        <v>1595</v>
+        <v>1592</v>
       </c>
       <c r="K2" t="s">
-        <v>1596</v>
+        <v>1593</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>1597</v>
+        <v>1594</v>
       </c>
     </row>
   </sheetData>
@@ -7526,12 +7632,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet112.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet113.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F708D57E-D932-48CF-900D-A44E8A17C969}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23" bestFit="1" customWidth="1"/>
@@ -7543,31 +7649,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>768</v>
+        <v>1624</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>769</v>
+        <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1597</v>
+      </c>
+      <c r="F1" t="s">
         <v>1598</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>1599</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>1600</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>1601</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1602</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1603</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -7578,29 +7684,288 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G2" t="s">
         <v>1605</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>1606</v>
       </c>
-      <c r="E2" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1605</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1608</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1609</v>
-      </c>
       <c r="I2" t="s">
-        <v>1605</v>
+        <v>1602</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet114.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F6C113-49E3-48C1-9E92-A45E06088FE5}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="31.140625" style="14" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1608</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>1611</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>1612</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>1613</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1619</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="N1" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46147</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46148</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>796</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>1615</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>1614</v>
+      </c>
+      <c r="K2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="L2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="N2" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet115.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263D3154-4E5B-463D-B04C-406ED24F60F5}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1630</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1633</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D2">
+        <v>1508910</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet116.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9666C3B-E460-4F27-BA43-9DDADC9D3599}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>901</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1638</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D2" s="14">
+        <v>1508844</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14220,7 +14585,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17114,7 +17479,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17234,7 +17599,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17309,7 +17674,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17364,7 +17729,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17449,7 +17814,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17588,7 +17953,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18035,7 +18400,7 @@
     <col min="16" max="16" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="23" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
@@ -18052,7 +18417,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18118,7 +18483,7 @@
         <v>1452</v>
       </c>
       <c r="W1" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="X1" t="s">
         <v>1453</v>
@@ -18142,7 +18507,7 @@
         <v>994</v>
       </c>
       <c r="AE1" t="s">
-        <v>1467</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -18195,37 +18560,37 @@
         <v>980</v>
       </c>
       <c r="Q2" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="R2" t="s">
         <v>219</v>
       </c>
       <c r="S2" t="s">
-        <v>1466</v>
+        <v>1636</v>
       </c>
       <c r="T2" t="s">
-        <v>1458</v>
+        <v>1625</v>
       </c>
       <c r="U2" t="s">
-        <v>1459</v>
+        <v>1637</v>
       </c>
       <c r="V2">
         <v>2</v>
       </c>
       <c r="W2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2" t="s">
         <v>1460</v>
       </c>
-      <c r="X2">
-        <v>5</v>
-      </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="AA2" t="s">
         <v>1462</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>1463</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1464</v>
       </c>
       <c r="AB2">
         <v>5</v>
@@ -18237,7 +18602,7 @@
         <v>997</v>
       </c>
       <c r="AE2" t="s">
-        <v>1468</v>
+        <v>1465</v>
       </c>
     </row>
   </sheetData>
@@ -18257,7 +18622,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18287,7 +18652,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18324,7 +18689,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>900</v>
+        <v>1624</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18333,22 +18698,22 @@
         <v>1336</v>
       </c>
       <c r="D1" t="s">
-        <v>1469</v>
+        <v>1466</v>
       </c>
       <c r="E1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F1" t="s">
         <v>1470</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I1" t="s">
         <v>1473</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1474</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1475</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -18362,10 +18727,10 @@
         <v>1508875</v>
       </c>
       <c r="D2" t="s">
-        <v>1472</v>
+        <v>1469</v>
       </c>
       <c r="E2" t="s">
-        <v>1471</v>
+        <v>1468</v>
       </c>
       <c r="F2">
         <v>4</v>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA2E10A-5C96-4922-8D1A-443751B0D922}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1672D97B-F0A1-441A-934A-96CAB0C28593}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="112" activeTab="115" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="88" activeTab="90" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="1642">
   <si>
     <t>SANITY HOSPITAL</t>
   </si>
@@ -4160,9 +4160,6 @@
     <t>SPSL.886284</t>
   </si>
   <si>
-    <t>19-03-20206</t>
-  </si>
-  <si>
     <t>select</t>
   </si>
   <si>
@@ -5058,6 +5055,12 @@
   </si>
   <si>
     <t>Missed Dose Remarks</t>
+  </si>
+  <si>
+    <t>Search_Patient_Frome_Date</t>
+  </si>
+  <si>
+    <t>Search_Patient_To_Date</t>
   </si>
 </sst>
 </file>
@@ -6029,19 +6032,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D1" t="s">
         <v>1474</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1475</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1476</v>
       </c>
       <c r="F1" t="s">
         <v>1257</v>
@@ -6070,7 +6073,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
   </sheetData>
@@ -6091,16 +6094,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="D1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6153,64 +6156,64 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D1" t="s">
         <v>1479</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1480</v>
       </c>
-      <c r="E1" t="s">
-        <v>1481</v>
-      </c>
       <c r="F1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="G1" t="s">
         <v>1253</v>
       </c>
       <c r="H1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="I1" t="s">
         <v>1482</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1483</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1484</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1485</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1486</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1487</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1488</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1489</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>1490</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1491</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1492</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1493</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1494</v>
       </c>
       <c r="U1" t="s">
         <v>604</v>
@@ -6236,13 +6239,13 @@
         <v>46128</v>
       </c>
       <c r="F2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="G2" t="s">
         <v>1495</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>1496</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1497</v>
       </c>
       <c r="I2">
         <v>50</v>
@@ -6263,10 +6266,10 @@
         <v>15</v>
       </c>
       <c r="O2" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="P2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="Q2" t="s">
         <v>15</v>
@@ -6275,7 +6278,7 @@
         <v>1224</v>
       </c>
       <c r="S2" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="T2">
         <v>5</v>
@@ -6308,19 +6311,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E1" t="s">
         <v>1500</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1480</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1501</v>
       </c>
       <c r="F1" t="s">
         <v>1336</v>
@@ -6343,7 +6346,7 @@
         <v>46128</v>
       </c>
       <c r="E2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="F2">
         <v>29578</v>
@@ -6372,16 +6375,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D1" t="s">
         <v>1503</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1504</v>
       </c>
       <c r="E1" t="s">
         <v>1336</v>
@@ -6404,7 +6407,7 @@
         <v>1258</v>
       </c>
       <c r="D2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E2">
         <v>1508888</v>
@@ -6438,7 +6441,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -6447,16 +6450,16 @@
         <v>920</v>
       </c>
       <c r="D1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F1" t="s">
         <v>925</v>
       </c>
       <c r="G1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6470,7 +6473,7 @@
         <v>927</v>
       </c>
       <c r="D2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="E2">
         <v>1508836</v>
@@ -6479,7 +6482,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
   </sheetData>
@@ -6502,22 +6505,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D1" t="s">
         <v>1509</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1510</v>
       </c>
-      <c r="E1" t="s">
-        <v>1511</v>
-      </c>
       <c r="F1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6534,7 +6537,7 @@
         <v>712</v>
       </c>
       <c r="E2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="F2">
         <v>1508858</v>
@@ -6569,52 +6572,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D1" t="s">
         <v>1348</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1349</v>
       </c>
       <c r="E1" t="s">
         <v>1336</v>
       </c>
       <c r="F1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G1" t="s">
         <v>1514</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1515</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1516</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K1" t="s">
         <v>1517</v>
       </c>
-      <c r="J1" t="s">
-        <v>1517</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1518</v>
       </c>
-      <c r="L1" t="s">
-        <v>1519</v>
-      </c>
       <c r="M1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="N1" t="s">
         <v>1524</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1525</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1526</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -6634,7 +6637,7 @@
         <v>1508858</v>
       </c>
       <c r="F2" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -6643,28 +6646,28 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J2" t="s">
         <v>1521</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1522</v>
       </c>
       <c r="K2">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="M2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="N2" t="s">
         <v>1528</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1529</v>
       </c>
       <c r="O2">
         <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
   </sheetData>
@@ -6694,22 +6697,22 @@
         <v>769</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>1531</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>1532</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>1533</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>1534</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>1535</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6720,7 +6723,7 @@
         <v>1202</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>932</v>
@@ -6729,7 +6732,7 @@
         <v>932</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>234</v>
@@ -7311,37 +7314,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D1" t="s">
         <v>1539</v>
       </c>
-      <c r="D1" t="s">
-        <v>1540</v>
-      </c>
       <c r="E1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>1549</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>1551</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>1550</v>
-      </c>
       <c r="H1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="I1" t="s">
         <v>1542</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1543</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1544</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -7352,31 +7355,31 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="D2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>1552</v>
+      </c>
+      <c r="H2" t="s">
         <v>1546</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>1552</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>1553</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1547</v>
       </c>
       <c r="I2">
         <v>45</v>
       </c>
       <c r="J2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="K2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
@@ -7410,58 +7413,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D1" t="s">
         <v>1554</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1555</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1556</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1557</v>
       </c>
-      <c r="G1" t="s">
-        <v>1558</v>
-      </c>
       <c r="H1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="I1" t="s">
         <v>1563</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1564</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1565</v>
       </c>
       <c r="K1" t="s">
         <v>604</v>
       </c>
       <c r="L1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="N1" t="s">
         <v>1566</v>
       </c>
-      <c r="M1" t="s">
-        <v>1572</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1567</v>
       </c>
-      <c r="O1" t="s">
-        <v>1568</v>
-      </c>
       <c r="P1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="R1" t="s">
         <v>1575</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>1575</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -7472,28 +7475,28 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D2" t="s">
         <v>1559</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1560</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1561</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="I2" t="s">
         <v>1569</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1570</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1571</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
@@ -7505,19 +7508,19 @@
         <v>8</v>
       </c>
       <c r="N2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="O2" t="s">
         <v>1573</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1574</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="R2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
   </sheetData>
@@ -7547,43 +7550,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="E1" t="s">
         <v>1579</v>
       </c>
-      <c r="D1" t="s">
-        <v>1581</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1580</v>
-      </c>
       <c r="F1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G1" t="s">
         <v>1585</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1586</v>
       </c>
       <c r="H1" t="s">
         <v>580</v>
       </c>
       <c r="I1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="J1" t="s">
         <v>1587</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1588</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1589</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1590</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -7594,13 +7597,13 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>1582</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1584</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1583</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7612,19 +7615,19 @@
         <v>219</v>
       </c>
       <c r="I2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="K2" t="s">
         <v>1592</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1593</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
   </sheetData>
@@ -7649,31 +7652,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D1" t="s">
         <v>1595</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1596</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1597</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1598</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1599</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1600</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -7684,25 +7687,25 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="D2" t="s">
         <v>1602</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1603</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G2" t="s">
         <v>1604</v>
       </c>
-      <c r="F2" t="s">
-        <v>1602</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>1605</v>
       </c>
-      <c r="H2" t="s">
-        <v>1606</v>
-      </c>
       <c r="I2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
   </sheetData>
@@ -7732,46 +7735,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>1606</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>1607</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>1608</v>
-      </c>
       <c r="G1" s="14" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>1610</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>1611</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>1612</v>
       </c>
-      <c r="J1" s="14" t="s">
-        <v>1613</v>
-      </c>
       <c r="K1" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="L1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="M1" t="s">
         <v>1619</v>
       </c>
-      <c r="M1" t="s">
-        <v>1620</v>
-      </c>
       <c r="N1" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -7791,31 +7794,31 @@
         <v>219</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>796</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>101</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="K2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="L2" t="s">
         <v>1617</v>
       </c>
-      <c r="L2" t="s">
-        <v>1618</v>
-      </c>
       <c r="M2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="N2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
   </sheetData>
@@ -7843,34 +7846,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D1" t="s">
         <v>1336</v>
       </c>
       <c r="E1" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F1" t="s">
         <v>1626</v>
       </c>
-      <c r="F1" t="s">
-        <v>1627</v>
-      </c>
       <c r="G1" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H1" t="s">
         <v>1629</v>
       </c>
-      <c r="H1" t="s">
-        <v>1630</v>
-      </c>
       <c r="I1" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J1" t="s">
         <v>1633</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -7881,28 +7884,28 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D2">
         <v>1508910</v>
       </c>
       <c r="E2" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="G2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H2" t="s">
         <v>1631</v>
       </c>
-      <c r="H2" t="s">
-        <v>1632</v>
-      </c>
       <c r="I2" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="J2" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
   </sheetData>
@@ -7925,22 +7928,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>1336</v>
       </c>
       <c r="E1" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F1" t="s">
         <v>1638</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7951,16 +7954,16 @@
         <v>1258</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D2" s="14">
         <v>1508844</v>
       </c>
       <c r="E2" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
   </sheetData>
@@ -14585,7 +14588,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -16975,10 +16978,10 @@
         <v>1320</v>
       </c>
       <c r="E2" t="s">
-        <v>1</v>
+        <v>191</v>
       </c>
       <c r="F2" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
         <v>1251</v>
@@ -17016,7 +17019,7 @@
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6369E9D3-38E6-4C79-8ECA-0C7BD071C1A0}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -17024,9 +17027,11 @@
     <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1208</v>
       </c>
@@ -17048,8 +17053,14 @@
       <c r="G1" t="s">
         <v>1339</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>1640</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -17060,16 +17071,22 @@
         <v>1340</v>
       </c>
       <c r="D2">
-        <v>1508821</v>
-      </c>
-      <c r="E2" t="s">
+        <v>1508836</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46153</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46154</v>
+      </c>
+      <c r="G2" t="s">
         <v>1341</v>
       </c>
-      <c r="F2" s="1">
-        <v>46100</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1342</v>
+      <c r="H2" s="1">
+        <v>46153</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
@@ -17133,7 +17150,7 @@
         <v>423</v>
       </c>
       <c r="E1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F1" t="s">
         <v>690</v>
@@ -17156,7 +17173,7 @@
         <v>46101</v>
       </c>
       <c r="E2" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F2" t="s">
         <v>1251</v>
@@ -17193,10 +17210,10 @@
         <v>10</v>
       </c>
       <c r="D1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E1" t="s">
         <v>1345</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -17207,10 +17224,10 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D2">
-        <v>1508824</v>
+        <v>1508925</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -17265,10 +17282,10 @@
         <v>1209</v>
       </c>
       <c r="C1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D1" t="s">
         <v>1348</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1349</v>
       </c>
       <c r="E1" t="s">
         <v>1336</v>
@@ -17417,7 +17434,7 @@
         <v>52416352</v>
       </c>
       <c r="U2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="V2" t="s">
         <v>8</v>
@@ -17450,7 +17467,7 @@
         <v>997</v>
       </c>
       <c r="AF2" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
   </sheetData>
@@ -17479,7 +17496,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17503,7 +17520,7 @@
         <v>936</v>
       </c>
       <c r="I1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="J1" t="s">
         <v>940</v>
@@ -17520,7 +17537,7 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D2">
         <v>1508832</v>
@@ -17544,7 +17561,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
   </sheetData>
@@ -17599,7 +17616,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17617,13 +17634,13 @@
         <v>450</v>
       </c>
       <c r="G1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H1" t="s">
         <v>956</v>
       </c>
       <c r="I1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -17634,19 +17651,19 @@
         <v>1219</v>
       </c>
       <c r="C2" s="1">
-        <v>46101</v>
+        <v>46090</v>
       </c>
       <c r="D2" s="1">
-        <v>46111</v>
+        <v>46093</v>
       </c>
       <c r="E2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F2">
         <v>1508832</v>
       </c>
       <c r="G2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -17674,7 +17691,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17683,10 +17700,10 @@
         <v>1336</v>
       </c>
       <c r="D1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E1" t="s">
         <v>1358</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -17703,7 +17720,7 @@
         <v>46111</v>
       </c>
       <c r="E2" s="1">
-        <v>46112</v>
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
@@ -17729,19 +17746,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="D1" t="s">
         <v>919</v>
       </c>
       <c r="E1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="F1" t="s">
         <v>433</v>
@@ -17750,10 +17767,10 @@
         <v>423</v>
       </c>
       <c r="H1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -17764,13 +17781,13 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D2" t="s">
         <v>1258</v>
       </c>
       <c r="E2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="F2" s="1">
         <v>46109</v>
@@ -17779,7 +17796,7 @@
         <v>46112</v>
       </c>
       <c r="H2" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="I2">
         <v>1508804</v>
@@ -17814,13 +17831,13 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D1" t="s">
         <v>1163</v>
@@ -17829,16 +17846,16 @@
         <v>424</v>
       </c>
       <c r="F1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G1" t="s">
         <v>1373</v>
       </c>
-      <c r="G1" t="s">
-        <v>1374</v>
-      </c>
       <c r="H1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="I1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="J1" t="s">
         <v>497</v>
@@ -17850,13 +17867,13 @@
         <v>499</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="N1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="O1" t="s">
         <v>1368</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -17903,7 +17920,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
   </sheetData>
@@ -17953,13 +17970,13 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D1" t="s">
         <v>1163</v>
@@ -17971,16 +17988,16 @@
         <v>1336</v>
       </c>
       <c r="G1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H1" t="s">
         <v>1375</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1376</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1377</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1378</v>
       </c>
       <c r="K1" t="s">
         <v>537</v>
@@ -17995,7 +18012,7 @@
         <v>499</v>
       </c>
       <c r="O1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="P1" t="s">
         <v>1167</v>
@@ -18004,49 +18021,49 @@
         <v>570</v>
       </c>
       <c r="R1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="S1" t="s">
         <v>1380</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1381</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1382</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1383</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1384</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1385</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1386</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1387</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1388</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1389</v>
       </c>
-      <c r="AB1" t="s">
-        <v>1390</v>
-      </c>
       <c r="AC1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AD1" t="s">
         <v>1423</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>1424</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>1425</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
@@ -18063,7 +18080,7 @@
         <v>46114</v>
       </c>
       <c r="E2" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F2">
         <v>1508844</v>
@@ -18135,13 +18152,13 @@
         <v>700</v>
       </c>
       <c r="AC2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AD2">
         <v>35628</v>
       </c>
       <c r="AE2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AF2">
         <v>800</v>
@@ -18194,91 +18211,91 @@
         <v>1336</v>
       </c>
       <c r="B1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C1" t="s">
         <v>1391</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1392</v>
       </c>
-      <c r="D1" t="s">
-        <v>1393</v>
-      </c>
       <c r="E1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F1" t="s">
         <v>1395</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1396</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1397</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1398</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1399</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1400</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1401</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1402</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1403</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1404</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1405</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>1406</v>
       </c>
-      <c r="Q1" t="s">
-        <v>1407</v>
-      </c>
       <c r="R1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="S1" t="s">
         <v>1083</v>
       </c>
       <c r="T1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="U1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="V1" t="s">
         <v>1413</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1414</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1415</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1416</v>
       </c>
       <c r="Y1" t="s">
         <v>1155</v>
       </c>
       <c r="Z1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AA1" t="s">
         <v>1417</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1418</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>1419</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>1420</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
@@ -18292,7 +18309,7 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E2">
         <v>56421</v>
@@ -18331,16 +18348,16 @@
         <v>15</v>
       </c>
       <c r="Q2" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="R2" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="S2" t="s">
         <v>1120</v>
       </c>
       <c r="T2" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="U2">
         <v>150</v>
@@ -18361,7 +18378,7 @@
         <v>120</v>
       </c>
       <c r="AA2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AB2">
         <v>63541</v>
@@ -18417,13 +18434,13 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D1" t="s">
         <v>1336</v>
@@ -18432,73 +18449,73 @@
         <v>278</v>
       </c>
       <c r="F1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H1" t="s">
         <v>1430</v>
       </c>
-      <c r="G1" t="s">
-        <v>1429</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1431</v>
-      </c>
       <c r="I1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="J1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="K1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="L1" t="s">
         <v>64</v>
       </c>
       <c r="M1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="N1" t="s">
         <v>1439</v>
       </c>
-      <c r="N1" t="s">
-        <v>1440</v>
-      </c>
       <c r="O1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="P1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="Q1" t="s">
         <v>1446</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1447</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1448</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1449</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1450</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1451</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="X1" t="s">
         <v>1452</v>
       </c>
-      <c r="W1" t="s">
-        <v>1459</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1453</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1454</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1455</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1456</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>1457</v>
       </c>
       <c r="AC1" t="s">
         <v>993</v>
@@ -18507,7 +18524,7 @@
         <v>994</v>
       </c>
       <c r="AE1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -18518,7 +18535,7 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="D2">
         <v>1508875</v>
@@ -18530,67 +18547,67 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="I2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="J2" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="M2" t="s">
         <v>1441</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>1442</v>
       </c>
-      <c r="N2" t="s">
-        <v>1443</v>
-      </c>
       <c r="O2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="P2" t="s">
         <v>980</v>
       </c>
       <c r="Q2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="R2" t="s">
         <v>219</v>
       </c>
       <c r="S2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="U2" t="s">
         <v>1636</v>
-      </c>
-      <c r="T2" t="s">
-        <v>1625</v>
-      </c>
-      <c r="U2" t="s">
-        <v>1637</v>
       </c>
       <c r="V2">
         <v>2</v>
       </c>
       <c r="W2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="X2">
         <v>3</v>
       </c>
       <c r="Y2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="Z2" t="s">
         <v>1460</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>1461</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1462</v>
       </c>
       <c r="AB2">
         <v>5</v>
@@ -18602,7 +18619,7 @@
         <v>997</v>
       </c>
       <c r="AE2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -18622,7 +18639,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18652,7 +18669,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18689,7 +18706,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18698,22 +18715,22 @@
         <v>1336</v>
       </c>
       <c r="D1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E1" t="s">
         <v>1466</v>
       </c>
-      <c r="E1" t="s">
-        <v>1467</v>
-      </c>
       <c r="F1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="G1" t="s">
         <v>1470</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1471</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1472</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -18727,10 +18744,10 @@
         <v>1508875</v>
       </c>
       <c r="D2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="E2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="F2">
         <v>4</v>

--- a/InputData/DataProvider_FrontOffice.xlsx
+++ b/InputData/DataProvider_FrontOffice.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1672D97B-F0A1-441A-934A-96CAB0C28593}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE5698A-9412-4003-B6B0-C164CCA40214}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="88" activeTab="90" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="92" activeTab="95" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FO_Registration_Page" sheetId="15" r:id="rId1"/>
@@ -4088,9 +4088,6 @@
     <t>Ambulanc Othetr Details Test</t>
   </si>
   <si>
-    <t>Shama</t>
-  </si>
-  <si>
     <t>Requested_Bed_Type_Drp</t>
   </si>
   <si>
@@ -5061,6 +5058,9 @@
   </si>
   <si>
     <t>Search_Patient_To_Date</t>
+  </si>
+  <si>
+    <t>ER_Station_Drp</t>
   </si>
 </sst>
 </file>
@@ -6032,19 +6032,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D1" t="s">
         <v>1473</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1474</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1475</v>
       </c>
       <c r="F1" t="s">
         <v>1257</v>
@@ -6073,7 +6073,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
   </sheetData>
@@ -6094,16 +6094,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="D1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -6156,70 +6156,70 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D1" t="s">
         <v>1478</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1479</v>
       </c>
-      <c r="E1" t="s">
-        <v>1480</v>
-      </c>
       <c r="F1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="G1" t="s">
         <v>1253</v>
       </c>
       <c r="H1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="I1" t="s">
         <v>1481</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1482</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1483</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1484</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1485</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1486</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1487</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1488</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>1489</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1490</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1491</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1492</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1493</v>
       </c>
       <c r="U1" t="s">
         <v>604</v>
       </c>
       <c r="V1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -6239,13 +6239,13 @@
         <v>46128</v>
       </c>
       <c r="F2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G2" t="s">
         <v>1494</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>1495</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1496</v>
       </c>
       <c r="I2">
         <v>50</v>
@@ -6266,10 +6266,10 @@
         <v>15</v>
       </c>
       <c r="O2" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="P2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="s">
         <v>15</v>
@@ -6278,7 +6278,7 @@
         <v>1224</v>
       </c>
       <c r="S2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="T2">
         <v>5</v>
@@ -6311,22 +6311,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E1" t="s">
         <v>1499</v>
       </c>
-      <c r="D1" t="s">
-        <v>1479</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1500</v>
-      </c>
       <c r="F1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G1" t="s">
         <v>1257</v>
@@ -6346,7 +6346,7 @@
         <v>46128</v>
       </c>
       <c r="E2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="F2">
         <v>29578</v>
@@ -6375,19 +6375,19 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D1" t="s">
         <v>1502</v>
       </c>
-      <c r="D1" t="s">
-        <v>1503</v>
-      </c>
       <c r="E1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F1" t="s">
         <v>433</v>
@@ -6407,7 +6407,7 @@
         <v>1258</v>
       </c>
       <c r="D2" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E2">
         <v>1508888</v>
@@ -6441,7 +6441,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -6450,16 +6450,16 @@
         <v>920</v>
       </c>
       <c r="D1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="F1" t="s">
         <v>925</v>
       </c>
       <c r="G1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6473,7 +6473,7 @@
         <v>927</v>
       </c>
       <c r="D2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E2">
         <v>1508836</v>
@@ -6482,7 +6482,7 @@
         <v>523</v>
       </c>
       <c r="G2" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
   </sheetData>
@@ -6505,22 +6505,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D1" t="s">
         <v>1508</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1509</v>
       </c>
-      <c r="E1" t="s">
-        <v>1510</v>
-      </c>
       <c r="F1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -6537,7 +6537,7 @@
         <v>712</v>
       </c>
       <c r="E2" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F2">
         <v>1508858</v>
@@ -6572,52 +6572,52 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D1" t="s">
         <v>1347</v>
       </c>
-      <c r="D1" t="s">
-        <v>1348</v>
-      </c>
       <c r="E1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="G1" t="s">
         <v>1513</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1514</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1515</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="K1" t="s">
         <v>1516</v>
       </c>
-      <c r="J1" t="s">
-        <v>1516</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1517</v>
       </c>
-      <c r="L1" t="s">
-        <v>1518</v>
-      </c>
       <c r="M1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N1" t="s">
         <v>1523</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1524</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1525</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -6637,7 +6637,7 @@
         <v>1508858</v>
       </c>
       <c r="F2" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="G2">
         <v>20</v>
@@ -6646,28 +6646,28 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J2" t="s">
         <v>1520</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1521</v>
       </c>
       <c r="K2">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="M2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="N2" t="s">
         <v>1527</v>
-      </c>
-      <c r="N2" t="s">
-        <v>1528</v>
       </c>
       <c r="O2">
         <v>5</v>
       </c>
       <c r="P2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
   </sheetData>
@@ -6697,22 +6697,22 @@
         <v>769</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>1530</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="E1" s="16" t="s">
         <v>1531</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="16" t="s">
         <v>1532</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>1533</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>1534</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -6723,7 +6723,7 @@
         <v>1202</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>932</v>
@@ -6732,7 +6732,7 @@
         <v>932</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>234</v>
@@ -7314,37 +7314,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D1" t="s">
         <v>1538</v>
       </c>
-      <c r="D1" t="s">
-        <v>1539</v>
-      </c>
       <c r="E1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>1548</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>1550</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>1549</v>
-      </c>
       <c r="H1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="I1" t="s">
         <v>1541</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1542</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1543</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -7355,31 +7355,31 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="D2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H2" t="s">
         <v>1545</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>1551</v>
-      </c>
-      <c r="G2" s="14" t="s">
-        <v>1552</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1546</v>
       </c>
       <c r="I2">
         <v>45</v>
       </c>
       <c r="J2" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="K2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
   </sheetData>
@@ -7413,58 +7413,58 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D1" t="s">
         <v>1553</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1554</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1555</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1556</v>
       </c>
-      <c r="G1" t="s">
-        <v>1557</v>
-      </c>
       <c r="H1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="I1" t="s">
         <v>1562</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1563</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1564</v>
       </c>
       <c r="K1" t="s">
         <v>604</v>
       </c>
       <c r="L1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="M1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N1" t="s">
         <v>1565</v>
       </c>
-      <c r="M1" t="s">
-        <v>1571</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1566</v>
       </c>
-      <c r="O1" t="s">
-        <v>1567</v>
-      </c>
       <c r="P1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="R1" t="s">
         <v>1574</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="R1" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -7475,28 +7475,28 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D2" t="s">
         <v>1558</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1559</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1560</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="I2" t="s">
         <v>1568</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>1569</v>
-      </c>
-      <c r="J2" t="s">
-        <v>1570</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
@@ -7508,19 +7508,19 @@
         <v>8</v>
       </c>
       <c r="N2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="O2" t="s">
         <v>1572</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1573</v>
       </c>
       <c r="P2">
         <v>5</v>
       </c>
       <c r="Q2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="R2" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
   </sheetData>
@@ -7550,43 +7550,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E1" t="s">
         <v>1578</v>
       </c>
-      <c r="D1" t="s">
-        <v>1580</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1579</v>
-      </c>
       <c r="F1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G1" t="s">
         <v>1584</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1585</v>
       </c>
       <c r="H1" t="s">
         <v>580</v>
       </c>
       <c r="I1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J1" t="s">
         <v>1586</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1587</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1588</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1589</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -7597,13 +7597,13 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E2" s="14" t="s">
         <v>1581</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1583</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1582</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7615,19 +7615,19 @@
         <v>219</v>
       </c>
       <c r="I2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="J2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="K2" t="s">
         <v>1591</v>
-      </c>
-      <c r="K2" t="s">
-        <v>1592</v>
       </c>
       <c r="L2">
         <v>4</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
     </row>
   </sheetData>
@@ -7652,31 +7652,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
+        <v>1593</v>
+      </c>
+      <c r="D1" t="s">
         <v>1594</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1595</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1596</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1597</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1598</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1599</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -7687,25 +7687,25 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D2" t="s">
         <v>1601</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1602</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G2" t="s">
         <v>1603</v>
       </c>
-      <c r="F2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>1604</v>
       </c>
-      <c r="H2" t="s">
-        <v>1605</v>
-      </c>
       <c r="I2" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
   </sheetData>
@@ -7735,46 +7735,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="E1" s="14" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>1606</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>1607</v>
-      </c>
       <c r="G1" s="14" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>1609</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>1610</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="14" t="s">
         <v>1611</v>
       </c>
-      <c r="J1" s="14" t="s">
-        <v>1612</v>
-      </c>
       <c r="K1" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="L1" t="s">
+        <v>1617</v>
+      </c>
+      <c r="M1" t="s">
         <v>1618</v>
       </c>
-      <c r="M1" t="s">
-        <v>1619</v>
-      </c>
       <c r="N1" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -7794,31 +7794,31 @@
         <v>219</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>796</v>
       </c>
       <c r="H2" s="14" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="I2" s="14" t="s">
         <v>101</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="K2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="L2" t="s">
         <v>1616</v>
       </c>
-      <c r="L2" t="s">
-        <v>1617</v>
-      </c>
       <c r="M2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="N2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
     </row>
   </sheetData>
@@ -7846,34 +7846,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E1" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F1" t="s">
         <v>1625</v>
       </c>
-      <c r="F1" t="s">
-        <v>1626</v>
-      </c>
       <c r="G1" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H1" t="s">
         <v>1628</v>
       </c>
-      <c r="H1" t="s">
-        <v>1629</v>
-      </c>
       <c r="I1" t="s">
+        <v>1631</v>
+      </c>
+      <c r="J1" t="s">
         <v>1632</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -7884,28 +7884,28 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D2">
         <v>1508910</v>
       </c>
       <c r="E2" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="G2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H2" t="s">
         <v>1630</v>
       </c>
-      <c r="H2" t="s">
-        <v>1631</v>
-      </c>
       <c r="I2" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="J2" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
   </sheetData>
@@ -7928,22 +7928,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>901</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E1" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F1" t="s">
         <v>1637</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -7954,16 +7954,16 @@
         <v>1258</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D2" s="14">
         <v>1508844</v>
       </c>
       <c r="E2" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
   </sheetData>
@@ -14588,7 +14588,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -16617,7 +16617,7 @@
         <v>712</v>
       </c>
       <c r="E2" t="s">
-        <v>1317</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
         <v>932</v>
@@ -16919,28 +16919,28 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B1" t="s">
         <v>1318</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1319</v>
       </c>
       <c r="C1" t="s">
         <v>1257</v>
       </c>
       <c r="D1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E1" t="s">
         <v>1321</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1322</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1323</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1324</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1325</v>
       </c>
       <c r="I1" t="s">
         <v>1250</v>
@@ -16949,19 +16949,19 @@
         <v>1252</v>
       </c>
       <c r="K1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="L1" t="s">
         <v>1328</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1329</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1330</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1331</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -16975,7 +16975,7 @@
         <v>1202</v>
       </c>
       <c r="D2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E2" t="s">
         <v>191</v>
@@ -16987,13 +16987,13 @@
         <v>1251</v>
       </c>
       <c r="H2" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I2" t="s">
         <v>796</v>
       </c>
       <c r="J2" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="K2" t="s">
         <v>1085</v>
@@ -17005,10 +17005,10 @@
         <v>8527419630</v>
       </c>
       <c r="N2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="O2" t="s">
         <v>1333</v>
-      </c>
-      <c r="O2" t="s">
-        <v>1334</v>
       </c>
     </row>
   </sheetData>
@@ -17039,25 +17039,25 @@
         <v>1209</v>
       </c>
       <c r="C1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D1" t="s">
         <v>1335</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1336</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1337</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1338</v>
       </c>
-      <c r="G1" t="s">
-        <v>1339</v>
-      </c>
       <c r="H1" t="s">
+        <v>1639</v>
+      </c>
+      <c r="I1" t="s">
         <v>1640</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -17068,7 +17068,7 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D2">
         <v>1508836</v>
@@ -17080,7 +17080,7 @@
         <v>46154</v>
       </c>
       <c r="G2" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="H2" s="1">
         <v>46153</v>
@@ -17150,7 +17150,7 @@
         <v>423</v>
       </c>
       <c r="E1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="F1" t="s">
         <v>690</v>
@@ -17173,7 +17173,7 @@
         <v>46101</v>
       </c>
       <c r="E2" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="s">
         <v>1251</v>
@@ -17210,10 +17210,10 @@
         <v>10</v>
       </c>
       <c r="D1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E1" t="s">
         <v>1344</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -17224,7 +17224,7 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="D2">
         <v>1508925</v>
@@ -17282,13 +17282,13 @@
         <v>1209</v>
       </c>
       <c r="C1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D1" t="s">
         <v>1347</v>
       </c>
-      <c r="D1" t="s">
-        <v>1348</v>
-      </c>
       <c r="E1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F1" t="s">
         <v>1006</v>
@@ -17434,7 +17434,7 @@
         <v>52416352</v>
       </c>
       <c r="U2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="V2" t="s">
         <v>8</v>
@@ -17467,7 +17467,7 @@
         <v>997</v>
       </c>
       <c r="AF2" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
   </sheetData>
@@ -17496,7 +17496,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17520,7 +17520,7 @@
         <v>936</v>
       </c>
       <c r="I1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="J1" t="s">
         <v>940</v>
@@ -17537,7 +17537,7 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D2">
         <v>1508832</v>
@@ -17561,7 +17561,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
   </sheetData>
@@ -17616,7 +17616,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -17634,13 +17634,13 @@
         <v>450</v>
       </c>
       <c r="G1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="H1" t="s">
         <v>956</v>
       </c>
       <c r="I1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -17657,13 +17657,13 @@
         <v>46093</v>
       </c>
       <c r="E2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F2">
         <v>1508832</v>
       </c>
       <c r="G2" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="H2">
         <v>2</v>
@@ -17691,19 +17691,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E1" t="s">
         <v>1357</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -17746,19 +17746,19 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D1" t="s">
         <v>919</v>
       </c>
       <c r="E1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="F1" t="s">
         <v>433</v>
@@ -17767,10 +17767,10 @@
         <v>423</v>
       </c>
       <c r="H1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -17781,13 +17781,13 @@
         <v>1219</v>
       </c>
       <c r="C2" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D2" t="s">
         <v>1258</v>
       </c>
       <c r="E2" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="F2" s="1">
         <v>46109</v>
@@ -17796,7 +17796,7 @@
         <v>46112</v>
       </c>
       <c r="H2" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="I2">
         <v>1508804</v>
@@ -17831,13 +17831,13 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
-        <v>901</v>
+        <v>1641</v>
       </c>
       <c r="C1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D1" t="s">
         <v>1163</v>
@@ -17846,16 +17846,16 @@
         <v>424</v>
       </c>
       <c r="F1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G1" t="s">
         <v>1372</v>
       </c>
-      <c r="G1" t="s">
-        <v>1373</v>
-      </c>
       <c r="H1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="I1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="J1" t="s">
         <v>497</v>
@@ -17867,13 +17867,13 @@
         <v>499</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="N1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="O1" t="s">
         <v>1367</v>
-      </c>
-      <c r="O1" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
@@ -17893,10 +17893,10 @@
         <v>216</v>
       </c>
       <c r="F2" s="1">
-        <v>46101</v>
+        <v>46042</v>
       </c>
       <c r="G2" s="1">
-        <v>46114</v>
+        <v>46155</v>
       </c>
       <c r="H2" s="13">
         <v>1508851</v>
@@ -17920,7 +17920,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
   </sheetData>
@@ -17937,7 +17937,7 @@
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
     <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -17970,13 +17970,13 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="D1" t="s">
         <v>1163</v>
@@ -17985,19 +17985,19 @@
         <v>10</v>
       </c>
       <c r="F1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H1" t="s">
         <v>1374</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1375</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1376</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1377</v>
       </c>
       <c r="K1" t="s">
         <v>537</v>
@@ -18012,7 +18012,7 @@
         <v>499</v>
       </c>
       <c r="O1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="P1" t="s">
         <v>1167</v>
@@ -18021,49 +18021,49 @@
         <v>570</v>
       </c>
       <c r="R1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="S1" t="s">
         <v>1379</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1380</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1381</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1382</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1383</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1384</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1385</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1386</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1387</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1388</v>
       </c>
-      <c r="AB1" t="s">
-        <v>1389</v>
-      </c>
       <c r="AC1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="AD1" t="s">
         <v>1422</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>1423</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>1424</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
@@ -18074,13 +18074,13 @@
         <v>1219</v>
       </c>
       <c r="C2" s="1">
-        <v>46111</v>
+        <v>46153</v>
       </c>
       <c r="D2" s="1">
-        <v>46114</v>
+        <v>46155</v>
       </c>
       <c r="E2" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F2">
         <v>1508844</v>
@@ -18113,10 +18113,10 @@
         <v>1508832</v>
       </c>
       <c r="P2" s="1">
-        <v>46114</v>
+        <v>46152</v>
       </c>
       <c r="Q2" s="1">
-        <v>46115</v>
+        <v>46155</v>
       </c>
       <c r="R2">
         <v>99999</v>
@@ -18152,13 +18152,13 @@
         <v>700</v>
       </c>
       <c r="AC2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AD2">
         <v>35628</v>
       </c>
       <c r="AE2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="AF2">
         <v>800</v>
@@ -18176,7 +18176,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.140625" bestFit="1" customWidth="1"/>
@@ -18208,108 +18208,108 @@
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C1" t="s">
         <v>1390</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1391</v>
       </c>
-      <c r="D1" t="s">
-        <v>1392</v>
-      </c>
       <c r="E1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F1" t="s">
         <v>1394</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>1395</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1396</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1397</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>1398</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>1399</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>1400</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>1401</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>1402</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>1403</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>1404</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>1405</v>
       </c>
-      <c r="Q1" t="s">
-        <v>1406</v>
-      </c>
       <c r="R1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="S1" t="s">
         <v>1083</v>
       </c>
       <c r="T1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="U1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="V1" t="s">
         <v>1412</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>1413</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>1414</v>
-      </c>
-      <c r="X1" t="s">
-        <v>1415</v>
       </c>
       <c r="Y1" t="s">
         <v>1155</v>
       </c>
       <c r="Z1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="AA1" t="s">
         <v>1416</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1417</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>1418</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>1419</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1508844</v>
       </c>
-      <c r="B2">
-        <v>300</v>
+      <c r="B2" s="14">
+        <v>500</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E2">
         <v>56421</v>
@@ -18324,7 +18324,7 @@
         <v>1120</v>
       </c>
       <c r="I2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J2">
         <v>52462</v>
@@ -18348,19 +18348,19 @@
         <v>15</v>
       </c>
       <c r="Q2" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="R2" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="S2" t="s">
         <v>1120</v>
       </c>
       <c r="T2" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="U2">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="V2">
         <v>56428</v>
@@ -18375,10 +18375,10 @@
         <v>8</v>
       </c>
       <c r="Z2">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AA2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AB2">
         <v>63541</v>
@@ -18387,7 +18387,7 @@
         <v>15</v>
       </c>
       <c r="AD2">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -18434,88 +18434,88 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E1" t="s">
         <v>278</v>
       </c>
       <c r="F1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H1" t="s">
         <v>1429</v>
       </c>
-      <c r="G1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1430</v>
-      </c>
       <c r="I1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="J1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="K1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="L1" t="s">
         <v>64</v>
       </c>
       <c r="M1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="N1" t="s">
         <v>1438</v>
       </c>
-      <c r="N1" t="s">
-        <v>1439</v>
-      </c>
       <c r="O1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="P1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="Q1" t="s">
         <v>1445</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>1446</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>1447</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>1448</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>1449</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>1450</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="X1" t="s">
         <v>1451</v>
       </c>
-      <c r="W1" t="s">
-        <v>1458</v>
-      </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>1452</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>1453</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>1454</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>1455</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>1456</v>
       </c>
       <c r="AC1" t="s">
         <v>993</v>
@@ -18524,7 +18524,7 @@
         <v>994</v>
       </c>
       <c r="AE1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -18535,10 +18535,10 @@
         <v>1258</v>
       </c>
       <c r="C2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D2">
-        <v>1508875</v>
+        <v>1508901</v>
       </c>
       <c r="E2" t="s">
         <v>219</v>
@@ -18547,67 +18547,67 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="I2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="J2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="K2">
         <v>2</v>
       </c>
       <c r="L2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="M2" t="s">
         <v>1440</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>1441</v>
       </c>
-      <c r="N2" t="s">
-        <v>1442</v>
-      </c>
       <c r="O2" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="P2" t="s">
         <v>980</v>
       </c>
       <c r="Q2" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="R2" t="s">
         <v>219</v>
       </c>
       <c r="S2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="U2" t="s">
         <v>1635</v>
-      </c>
-      <c r="T2" t="s">
-        <v>1624</v>
-      </c>
-      <c r="U2" t="s">
-        <v>1636</v>
       </c>
       <c r="V2">
         <v>2</v>
       </c>
       <c r="W2" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="X2">
         <v>3</v>
       </c>
       <c r="Y2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="Z2" t="s">
         <v>1459</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>1460</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>1461</v>
       </c>
       <c r="AB2">
         <v>5</v>
@@ -18619,7 +18619,7 @@
         <v>997</v>
       </c>
       <c r="AE2" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
   </sheetData>
@@ -18639,7 +18639,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18669,7 +18669,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
@@ -18706,31 +18706,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B1" t="s">
         <v>901</v>
       </c>
       <c r="C1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E1" t="s">
         <v>1465</v>
       </c>
-      <c r="E1" t="s">
-        <v>1466</v>
-      </c>
       <c r="F1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="G1" t="s">
         <v>1469</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>1470</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>1471</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -18744,10 +18744,10 @@
         <v>1508875</v>
       </c>
       <c r="D2" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="E2" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F2">
         <v>4</v>
